--- a/research/traditional_assets/database/data/turkey/turkey_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_aerospace_defense.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ibse_asels" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.423</v>
+        <v>0.403</v>
       </c>
       <c r="E2">
-        <v>0.588</v>
+        <v>0.532</v>
       </c>
       <c r="G2">
-        <v>0.2839140103780578</v>
+        <v>0.3039973127309372</v>
       </c>
       <c r="H2">
-        <v>0.2609340252038547</v>
+        <v>0.2861941551897884</v>
       </c>
       <c r="I2">
-        <v>0.2323202372127502</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="J2">
-        <v>0.2260755391072195</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="K2">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="L2">
-        <v>0.2559920929083271</v>
+        <v>0.3547195162915687</v>
       </c>
       <c r="M2">
-        <v>15.8</v>
+        <v>5.58</v>
       </c>
       <c r="N2">
-        <v>0.004381950800122029</v>
+        <v>0.0007368671262182078</v>
       </c>
       <c r="O2">
-        <v>0.0305019305019305</v>
+        <v>0.01056818181818182</v>
       </c>
       <c r="P2">
-        <v>15.8</v>
+        <v>5.58</v>
       </c>
       <c r="Q2">
-        <v>0.004381950800122029</v>
+        <v>0.0007368671262182078</v>
       </c>
       <c r="R2">
-        <v>0.0305019305019305</v>
+        <v>0.01056818181818182</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,70 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>147.6</v>
+        <v>73</v>
       </c>
       <c r="V2">
-        <v>0.04093518595557034</v>
+        <v>0.009640017959485513</v>
       </c>
       <c r="W2">
-        <v>0.2476099426386233</v>
+        <v>0.2274685507496123</v>
       </c>
       <c r="X2">
-        <v>0.1305970415636356</v>
+        <v>0.2294230859151024</v>
       </c>
       <c r="Y2">
-        <v>0.1170129010749878</v>
+        <v>-0.001954535165490101</v>
       </c>
       <c r="Z2">
-        <v>0.8939300229722567</v>
+        <v>0.5671124318969788</v>
       </c>
       <c r="AA2">
-        <v>0.202095711867582</v>
+        <v>0.1308720996685336</v>
       </c>
       <c r="AB2">
-        <v>0.1223173185446424</v>
+        <v>0.2218413255307888</v>
       </c>
       <c r="AC2">
-        <v>0.07977839332293968</v>
+        <v>-0.09096922586225525</v>
       </c>
       <c r="AD2">
-        <v>451.1</v>
+        <v>485.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>451.1</v>
+        <v>485.5</v>
       </c>
       <c r="AG2">
-        <v>303.5</v>
+        <v>412.5</v>
       </c>
       <c r="AH2">
-        <v>0.1111960165647801</v>
+        <v>0.0602499348481652</v>
       </c>
       <c r="AI2">
-        <v>0.1609519392014843</v>
+        <v>0.224498289096458</v>
       </c>
       <c r="AJ2">
-        <v>0.07763736825949044</v>
+        <v>0.05165871435548709</v>
       </c>
       <c r="AK2">
-        <v>0.1143083123046213</v>
+        <v>0.197406202143951</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>45.7</v>
       </c>
       <c r="AM2">
-        <v>-15.7</v>
+        <v>43.03</v>
       </c>
       <c r="AN2">
-        <v>0.8798517651648137</v>
+        <v>1.302656291923799</v>
+      </c>
+      <c r="AO2">
+        <v>7.516411378555798</v>
       </c>
       <c r="AP2">
-        <v>0.591964111566218</v>
+        <v>1.106788301583043</v>
       </c>
       <c r="AQ2">
-        <v>-29.94267515923567</v>
+        <v>7.982802695793632</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.423</v>
+        <v>0.403</v>
       </c>
       <c r="E3">
-        <v>0.588</v>
+        <v>0.532</v>
       </c>
       <c r="G3">
-        <v>0.2839140103780578</v>
+        <v>0.3039973127309372</v>
       </c>
       <c r="H3">
-        <v>0.2609340252038547</v>
+        <v>0.2861941551897884</v>
       </c>
       <c r="I3">
-        <v>0.2323202372127502</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="J3">
-        <v>0.2260755391072195</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="K3">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="L3">
-        <v>0.2559920929083271</v>
+        <v>0.3547195162915687</v>
       </c>
       <c r="M3">
-        <v>15.8</v>
+        <v>5.58</v>
       </c>
       <c r="N3">
-        <v>0.004381950800122029</v>
+        <v>0.0007368671262182078</v>
       </c>
       <c r="O3">
-        <v>0.0305019305019305</v>
+        <v>0.01056818181818182</v>
       </c>
       <c r="P3">
-        <v>15.8</v>
+        <v>5.58</v>
       </c>
       <c r="Q3">
-        <v>0.004381950800122029</v>
+        <v>0.0007368671262182078</v>
       </c>
       <c r="R3">
-        <v>0.0305019305019305</v>
+        <v>0.01056818181818182</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,70 +772,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>147.6</v>
+        <v>73</v>
       </c>
       <c r="V3">
-        <v>0.04093518595557034</v>
+        <v>0.009640017959485513</v>
       </c>
       <c r="W3">
-        <v>0.2476099426386233</v>
+        <v>0.2274685507496123</v>
       </c>
       <c r="X3">
-        <v>0.1305970415636356</v>
+        <v>0.2294230859151024</v>
       </c>
       <c r="Y3">
-        <v>0.1170129010749878</v>
+        <v>-0.001954535165490101</v>
       </c>
       <c r="Z3">
-        <v>0.8939300229722567</v>
+        <v>0.5671124318969788</v>
       </c>
       <c r="AA3">
-        <v>0.202095711867582</v>
+        <v>0.1308720996685336</v>
       </c>
       <c r="AB3">
-        <v>0.1223173185446424</v>
+        <v>0.2218413255307888</v>
       </c>
       <c r="AC3">
-        <v>0.07977839332293968</v>
+        <v>-0.09096922586225525</v>
       </c>
       <c r="AD3">
-        <v>451.1</v>
+        <v>485.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>451.1</v>
+        <v>485.5</v>
       </c>
       <c r="AG3">
-        <v>303.5</v>
+        <v>412.5</v>
       </c>
       <c r="AH3">
-        <v>0.1111960165647801</v>
+        <v>0.0602499348481652</v>
       </c>
       <c r="AI3">
-        <v>0.1609519392014843</v>
+        <v>0.224498289096458</v>
       </c>
       <c r="AJ3">
-        <v>0.07763736825949044</v>
+        <v>0.05165871435548709</v>
       </c>
       <c r="AK3">
-        <v>0.1143083123046213</v>
+        <v>0.197406202143951</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>45.7</v>
       </c>
       <c r="AM3">
-        <v>-15.7</v>
+        <v>43.03</v>
       </c>
       <c r="AN3">
-        <v>0.8798517651648137</v>
+        <v>1.302656291923799</v>
+      </c>
+      <c r="AO3">
+        <v>7.516411378555798</v>
       </c>
       <c r="AP3">
-        <v>0.591964111566218</v>
+        <v>1.106788301583043</v>
       </c>
       <c r="AQ3">
-        <v>-29.94267515923567</v>
+        <v>7.982802695793632</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aselsan Elektronik Sanayi ve Ticaret Anonim Sirketi (IBSE:ASELS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IBSE:ASELS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Aerospace/Defense</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0602499348481652</v>
+      </c>
+      <c r="F2">
+        <v>0.28</v>
+      </c>
+      <c r="G2">
+        <v>7572.6</v>
+      </c>
+      <c r="H2">
+        <v>6325.8029828557</v>
+      </c>
+      <c r="I2">
+        <v>7985.1</v>
+      </c>
+      <c r="J2">
+        <v>8509.070982855699</v>
+      </c>
+      <c r="K2">
+        <v>485.5</v>
+      </c>
+      <c r="L2">
+        <v>2256.268</v>
+      </c>
+      <c r="M2">
+        <v>0.221841325530789</v>
+      </c>
+      <c r="N2">
+        <v>0.210570019481654</v>
+      </c>
+      <c r="O2">
+        <v>0.103584603211009</v>
+      </c>
+      <c r="P2">
+        <v>0.045276</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.229423085915102</v>
+      </c>
+      <c r="T2">
+        <v>0.274851027057853</v>
+      </c>
+      <c r="U2">
+        <v>1.11265339561915</v>
+      </c>
+      <c r="V2">
+        <v>1.37781305729298</v>
+      </c>
+      <c r="W2">
+        <v>2.589159060312816</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>7572.6</v>
+      </c>
+      <c r="AB2">
+        <v>0.1713229714353474</v>
+      </c>
+      <c r="AC2">
+        <v>0.1345254587155963</v>
+      </c>
+      <c r="AD2">
+        <v>0.23</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>372.7</v>
+      </c>
+      <c r="AH2">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="AI2">
+        <v>144.9</v>
+      </c>
+      <c r="AJ2">
+        <v>485.5</v>
+      </c>
+      <c r="AK2">
+        <v>485.5</v>
+      </c>
+      <c r="AL2">
+        <v>45.7</v>
+      </c>
+      <c r="AM2">
+        <v>485.5</v>
+      </c>
+      <c r="AN2">
+        <v>73</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.2204553436101478</v>
+      </c>
+      <c r="C2">
+        <v>8119.024187610259</v>
+      </c>
+      <c r="D2">
+        <v>8046.024187610259</v>
+      </c>
+      <c r="E2">
+        <v>-485.5</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>73</v>
+      </c>
+      <c r="H2">
+        <v>7572.6</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>372.7</v>
+      </c>
+      <c r="K2">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L2">
+        <v>343.5</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>343.5</v>
+      </c>
+      <c r="O2">
+        <v>79.005</v>
+      </c>
+      <c r="P2">
+        <v>264.495</v>
+      </c>
+      <c r="Q2">
+        <v>293.695</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.2204553436101478</v>
+      </c>
+      <c r="T2">
+        <v>1.060309321559365</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.23</v>
+      </c>
+      <c r="W2">
+        <v>0.035189</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.2200014263198444</v>
+      </c>
+      <c r="C3">
+        <v>8058.598820880544</v>
+      </c>
+      <c r="D3">
+        <v>8066.179820880544</v>
+      </c>
+      <c r="E3">
+        <v>-404.919</v>
+      </c>
+      <c r="F3">
+        <v>80.581</v>
+      </c>
+      <c r="G3">
+        <v>73</v>
+      </c>
+      <c r="H3">
+        <v>7572.6</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>372.7</v>
+      </c>
+      <c r="K3">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L3">
+        <v>343.5</v>
+      </c>
+      <c r="M3">
+        <v>3.6825517</v>
+      </c>
+      <c r="N3">
+        <v>339.8174483</v>
+      </c>
+      <c r="O3">
+        <v>78.158013109</v>
+      </c>
+      <c r="P3">
+        <v>261.6594351910001</v>
+      </c>
+      <c r="Q3">
+        <v>290.859435191</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.2218682185048934</v>
+      </c>
+      <c r="T3">
+        <v>1.06855617183816</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.23</v>
+      </c>
+      <c r="W3">
+        <v>0.035189</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>93.27771284242934</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.2195475090295411</v>
+      </c>
+      <c r="C4">
+        <v>7998.274689188449</v>
+      </c>
+      <c r="D4">
+        <v>8086.436689188449</v>
+      </c>
+      <c r="E4">
+        <v>-324.338</v>
+      </c>
+      <c r="F4">
+        <v>161.162</v>
+      </c>
+      <c r="G4">
+        <v>73</v>
+      </c>
+      <c r="H4">
+        <v>7572.6</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>372.7</v>
+      </c>
+      <c r="K4">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L4">
+        <v>343.5</v>
+      </c>
+      <c r="M4">
+        <v>7.365103400000001</v>
+      </c>
+      <c r="N4">
+        <v>336.1348966</v>
+      </c>
+      <c r="O4">
+        <v>77.31102621799999</v>
+      </c>
+      <c r="P4">
+        <v>258.823870382</v>
+      </c>
+      <c r="Q4">
+        <v>288.023870382</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.2233099275811644</v>
+      </c>
+      <c r="T4">
+        <v>1.07697132518387</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.23</v>
+      </c>
+      <c r="W4">
+        <v>0.035189</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>46.63885642121466</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.2190935917392378</v>
+      </c>
+      <c r="C5">
+        <v>7938.052557159057</v>
+      </c>
+      <c r="D5">
+        <v>8106.795557159057</v>
+      </c>
+      <c r="E5">
+        <v>-243.757</v>
+      </c>
+      <c r="F5">
+        <v>241.743</v>
+      </c>
+      <c r="G5">
+        <v>73</v>
+      </c>
+      <c r="H5">
+        <v>7572.6</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>372.7</v>
+      </c>
+      <c r="K5">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L5">
+        <v>343.5</v>
+      </c>
+      <c r="M5">
+        <v>11.0476551</v>
+      </c>
+      <c r="N5">
+        <v>332.4523449</v>
+      </c>
+      <c r="O5">
+        <v>76.46403932699999</v>
+      </c>
+      <c r="P5">
+        <v>255.988305573</v>
+      </c>
+      <c r="Q5">
+        <v>285.188305573</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.2247813626177709</v>
+      </c>
+      <c r="T5">
+        <v>1.085559986845985</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.23</v>
+      </c>
+      <c r="W5">
+        <v>0.035189</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>31.09257094747645</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.2186396744489344</v>
+      </c>
+      <c r="C6">
+        <v>7877.933197137137</v>
+      </c>
+      <c r="D6">
+        <v>8127.257197137136</v>
+      </c>
+      <c r="E6">
+        <v>-163.176</v>
+      </c>
+      <c r="F6">
+        <v>322.324</v>
+      </c>
+      <c r="G6">
+        <v>73</v>
+      </c>
+      <c r="H6">
+        <v>7572.6</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>372.7</v>
+      </c>
+      <c r="K6">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L6">
+        <v>343.5</v>
+      </c>
+      <c r="M6">
+        <v>14.7302068</v>
+      </c>
+      <c r="N6">
+        <v>328.7697932</v>
+      </c>
+      <c r="O6">
+        <v>75.61705243599999</v>
+      </c>
+      <c r="P6">
+        <v>253.152740764</v>
+      </c>
+      <c r="Q6">
+        <v>282.352740764</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.2262834525509733</v>
+      </c>
+      <c r="T6">
+        <v>1.094327578959395</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.23</v>
+      </c>
+      <c r="W6">
+        <v>0.035189</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>23.31942821060733</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.2181857571586311</v>
+      </c>
+      <c r="C7">
+        <v>7817.917389284808</v>
+      </c>
+      <c r="D7">
+        <v>8147.822389284807</v>
+      </c>
+      <c r="E7">
+        <v>-82.59499999999997</v>
+      </c>
+      <c r="F7">
+        <v>402.905</v>
+      </c>
+      <c r="G7">
+        <v>73</v>
+      </c>
+      <c r="H7">
+        <v>7572.6</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>372.7</v>
+      </c>
+      <c r="K7">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L7">
+        <v>343.5</v>
+      </c>
+      <c r="M7">
+        <v>18.4127585</v>
+      </c>
+      <c r="N7">
+        <v>325.0872415</v>
+      </c>
+      <c r="O7">
+        <v>74.77006554499999</v>
+      </c>
+      <c r="P7">
+        <v>250.317175955</v>
+      </c>
+      <c r="Q7">
+        <v>279.517175955</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.227817165430138</v>
+      </c>
+      <c r="T7">
+        <v>1.103279751959403</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.23</v>
+      </c>
+      <c r="W7">
+        <v>0.035189</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>18.65554256848587</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.2177318398683277</v>
+      </c>
+      <c r="C8">
+        <v>7758.005921680712</v>
+      </c>
+      <c r="D8">
+        <v>8168.491921680712</v>
+      </c>
+      <c r="E8">
+        <v>-2.01400000000001</v>
+      </c>
+      <c r="F8">
+        <v>483.486</v>
+      </c>
+      <c r="G8">
+        <v>73</v>
+      </c>
+      <c r="H8">
+        <v>7572.6</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>372.7</v>
+      </c>
+      <c r="K8">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L8">
+        <v>343.5</v>
+      </c>
+      <c r="M8">
+        <v>22.0953102</v>
+      </c>
+      <c r="N8">
+        <v>321.4046898</v>
+      </c>
+      <c r="O8">
+        <v>73.92307865399999</v>
+      </c>
+      <c r="P8">
+        <v>247.481611146</v>
+      </c>
+      <c r="Q8">
+        <v>276.681611146</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.229383510498221</v>
+      </c>
+      <c r="T8">
+        <v>1.112422396725368</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.23</v>
+      </c>
+      <c r="W8">
+        <v>0.035189</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>15.54628547373822</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.2172779225780244</v>
+      </c>
+      <c r="C9">
+        <v>7698.19959042067</v>
+      </c>
+      <c r="D9">
+        <v>8189.266590420669</v>
+      </c>
+      <c r="E9">
+        <v>78.56700000000012</v>
+      </c>
+      <c r="F9">
+        <v>564.0670000000001</v>
+      </c>
+      <c r="G9">
+        <v>73</v>
+      </c>
+      <c r="H9">
+        <v>7572.6</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>372.7</v>
+      </c>
+      <c r="K9">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L9">
+        <v>343.5</v>
+      </c>
+      <c r="M9">
+        <v>25.77786190000001</v>
+      </c>
+      <c r="N9">
+        <v>317.7221381</v>
+      </c>
+      <c r="O9">
+        <v>73.07609176299999</v>
+      </c>
+      <c r="P9">
+        <v>244.646046337</v>
+      </c>
+      <c r="Q9">
+        <v>273.846046337</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.2309835404064778</v>
+      </c>
+      <c r="T9">
+        <v>1.121761657507806</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.23</v>
+      </c>
+      <c r="W9">
+        <v>0.035189</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>13.32538754891847</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.216824005287721</v>
+      </c>
+      <c r="C10">
+        <v>7638.499199719889</v>
+      </c>
+      <c r="D10">
+        <v>8210.14719971989</v>
+      </c>
+      <c r="E10">
+        <v>159.148</v>
+      </c>
+      <c r="F10">
+        <v>644.648</v>
+      </c>
+      <c r="G10">
+        <v>73</v>
+      </c>
+      <c r="H10">
+        <v>7572.6</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>372.7</v>
+      </c>
+      <c r="K10">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L10">
+        <v>343.5</v>
+      </c>
+      <c r="M10">
+        <v>29.4604136</v>
+      </c>
+      <c r="N10">
+        <v>314.0395864</v>
+      </c>
+      <c r="O10">
+        <v>72.22910487199999</v>
+      </c>
+      <c r="P10">
+        <v>241.810481528</v>
+      </c>
+      <c r="Q10">
+        <v>271.010481528</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.2326183535736098</v>
+      </c>
+      <c r="T10">
+        <v>1.131303945698557</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.23</v>
+      </c>
+      <c r="W10">
+        <v>0.035189</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>11.65971410530367</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.2163700879974177</v>
+      </c>
+      <c r="C11">
+        <v>7578.905562016756</v>
+      </c>
+      <c r="D11">
+        <v>8231.134562016756</v>
+      </c>
+      <c r="E11">
+        <v>239.729</v>
+      </c>
+      <c r="F11">
+        <v>725.229</v>
+      </c>
+      <c r="G11">
+        <v>73</v>
+      </c>
+      <c r="H11">
+        <v>7572.6</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>372.7</v>
+      </c>
+      <c r="K11">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L11">
+        <v>343.5</v>
+      </c>
+      <c r="M11">
+        <v>33.14296530000001</v>
+      </c>
+      <c r="N11">
+        <v>310.3570347</v>
+      </c>
+      <c r="O11">
+        <v>71.38211798099999</v>
+      </c>
+      <c r="P11">
+        <v>238.974916719</v>
+      </c>
+      <c r="Q11">
+        <v>268.174916719</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.2342890967004591</v>
+      </c>
+      <c r="T11">
+        <v>1.141055954508886</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.23</v>
+      </c>
+      <c r="W11">
+        <v>0.035189</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>10.36419031582548</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.2159161707071144</v>
+      </c>
+      <c r="C12">
+        <v>7519.419498078191</v>
+      </c>
+      <c r="D12">
+        <v>8252.229498078192</v>
+      </c>
+      <c r="E12">
+        <v>320.3100000000001</v>
+      </c>
+      <c r="F12">
+        <v>805.8100000000001</v>
+      </c>
+      <c r="G12">
+        <v>73</v>
+      </c>
+      <c r="H12">
+        <v>7572.6</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>372.7</v>
+      </c>
+      <c r="K12">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L12">
+        <v>343.5</v>
+      </c>
+      <c r="M12">
+        <v>36.825517</v>
+      </c>
+      <c r="N12">
+        <v>306.674483</v>
+      </c>
+      <c r="O12">
+        <v>70.53513108999999</v>
+      </c>
+      <c r="P12">
+        <v>236.13935191</v>
+      </c>
+      <c r="Q12">
+        <v>265.33935191</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.2359969674523493</v>
+      </c>
+      <c r="T12">
+        <v>1.151024674626111</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.23</v>
+      </c>
+      <c r="W12">
+        <v>0.035189</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>9.327771284242933</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.2155977734168111</v>
+      </c>
+      <c r="C13">
+        <v>7453.700039942494</v>
+      </c>
+      <c r="D13">
+        <v>8267.091039942494</v>
+      </c>
+      <c r="E13">
+        <v>400.8910000000001</v>
+      </c>
+      <c r="F13">
+        <v>886.3910000000001</v>
+      </c>
+      <c r="G13">
+        <v>73</v>
+      </c>
+      <c r="H13">
+        <v>7572.6</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>372.7</v>
+      </c>
+      <c r="K13">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L13">
+        <v>343.5</v>
+      </c>
+      <c r="M13">
+        <v>41.9262943</v>
+      </c>
+      <c r="N13">
+        <v>301.5737057</v>
+      </c>
+      <c r="O13">
+        <v>69.361952311</v>
+      </c>
+      <c r="P13">
+        <v>232.211753389</v>
+      </c>
+      <c r="Q13">
+        <v>261.411753389</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.2377432173222596</v>
+      </c>
+      <c r="T13">
+        <v>1.161217410925745</v>
+      </c>
+      <c r="U13">
+        <v>0.0473</v>
+      </c>
+      <c r="V13">
+        <v>0.23</v>
+      </c>
+      <c r="W13">
+        <v>0.036421</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>8.192949215642937</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.2151561761265077</v>
+      </c>
+      <c r="C14">
+        <v>7393.819902719826</v>
+      </c>
+      <c r="D14">
+        <v>8287.791902719826</v>
+      </c>
+      <c r="E14">
+        <v>481.472</v>
+      </c>
+      <c r="F14">
+        <v>966.972</v>
+      </c>
+      <c r="G14">
+        <v>73</v>
+      </c>
+      <c r="H14">
+        <v>7572.6</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>372.7</v>
+      </c>
+      <c r="K14">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L14">
+        <v>343.5</v>
+      </c>
+      <c r="M14">
+        <v>45.7377756</v>
+      </c>
+      <c r="N14">
+        <v>297.7622244</v>
+      </c>
+      <c r="O14">
+        <v>68.48531161199999</v>
+      </c>
+      <c r="P14">
+        <v>229.276912788</v>
+      </c>
+      <c r="Q14">
+        <v>258.476912788</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.2395291546892133</v>
+      </c>
+      <c r="T14">
+        <v>1.171641800323099</v>
+      </c>
+      <c r="U14">
+        <v>0.0473</v>
+      </c>
+      <c r="V14">
+        <v>0.23</v>
+      </c>
+      <c r="W14">
+        <v>0.036421</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>7.510203447672693</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.2150949588362044</v>
+      </c>
+      <c r="C15">
+        <v>7316.116785140468</v>
+      </c>
+      <c r="D15">
+        <v>8290.669785140468</v>
+      </c>
+      <c r="E15">
+        <v>562.0530000000001</v>
+      </c>
+      <c r="F15">
+        <v>1047.553</v>
+      </c>
+      <c r="G15">
+        <v>73</v>
+      </c>
+      <c r="H15">
+        <v>7572.6</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>372.7</v>
+      </c>
+      <c r="K15">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L15">
+        <v>343.5</v>
+      </c>
+      <c r="M15">
+        <v>53.5299583</v>
+      </c>
+      <c r="N15">
+        <v>289.9700417</v>
+      </c>
+      <c r="O15">
+        <v>66.693109591</v>
+      </c>
+      <c r="P15">
+        <v>223.276932109</v>
+      </c>
+      <c r="Q15">
+        <v>252.476932109</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.2413561480875912</v>
+      </c>
+      <c r="T15">
+        <v>1.182305830856023</v>
+      </c>
+      <c r="U15">
+        <v>0.0511</v>
+      </c>
+      <c r="V15">
+        <v>0.23</v>
+      </c>
+      <c r="W15">
+        <v>0.039347</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>6.416967449795305</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.214682621545901</v>
+      </c>
+      <c r="C16">
+        <v>7254.972340520171</v>
+      </c>
+      <c r="D16">
+        <v>8310.106340520171</v>
+      </c>
+      <c r="E16">
+        <v>642.6340000000002</v>
+      </c>
+      <c r="F16">
+        <v>1128.134</v>
+      </c>
+      <c r="G16">
+        <v>73</v>
+      </c>
+      <c r="H16">
+        <v>7572.6</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>372.7</v>
+      </c>
+      <c r="K16">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L16">
+        <v>343.5</v>
+      </c>
+      <c r="M16">
+        <v>57.64764740000001</v>
+      </c>
+      <c r="N16">
+        <v>285.8523526</v>
+      </c>
+      <c r="O16">
+        <v>65.74604109799999</v>
+      </c>
+      <c r="P16">
+        <v>220.106311502</v>
+      </c>
+      <c r="Q16">
+        <v>249.306311502</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.243225629704536</v>
+      </c>
+      <c r="T16">
+        <v>1.193217862099016</v>
+      </c>
+      <c r="U16">
+        <v>0.0511</v>
+      </c>
+      <c r="V16">
+        <v>0.23</v>
+      </c>
+      <c r="W16">
+        <v>0.039347</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>5.958612631952782</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.2144897342555977</v>
+      </c>
+      <c r="C17">
+        <v>7183.514889491016</v>
+      </c>
+      <c r="D17">
+        <v>8319.229889491016</v>
+      </c>
+      <c r="E17">
+        <v>723.2149999999999</v>
+      </c>
+      <c r="F17">
+        <v>1208.715</v>
+      </c>
+      <c r="G17">
+        <v>73</v>
+      </c>
+      <c r="H17">
+        <v>7572.6</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>372.7</v>
+      </c>
+      <c r="K17">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L17">
+        <v>343.5</v>
+      </c>
+      <c r="M17">
+        <v>64.06189500000001</v>
+      </c>
+      <c r="N17">
+        <v>279.438105</v>
+      </c>
+      <c r="O17">
+        <v>64.27076414999999</v>
+      </c>
+      <c r="P17">
+        <v>215.16734085</v>
+      </c>
+      <c r="Q17">
+        <v>244.36734085</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.2451390991242326</v>
+      </c>
+      <c r="T17">
+        <v>1.204386647018314</v>
+      </c>
+      <c r="U17">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V17">
+        <v>0.23</v>
+      </c>
+      <c r="W17">
+        <v>0.04081000000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>5.362001857734617</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.2140920269652943</v>
+      </c>
+      <c r="C18">
+        <v>7121.808783198618</v>
+      </c>
+      <c r="D18">
+        <v>8338.104783198618</v>
+      </c>
+      <c r="E18">
+        <v>803.796</v>
+      </c>
+      <c r="F18">
+        <v>1289.296</v>
+      </c>
+      <c r="G18">
+        <v>73</v>
+      </c>
+      <c r="H18">
+        <v>7572.6</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>372.7</v>
+      </c>
+      <c r="K18">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L18">
+        <v>343.5</v>
+      </c>
+      <c r="M18">
+        <v>68.332688</v>
+      </c>
+      <c r="N18">
+        <v>275.167312</v>
+      </c>
+      <c r="O18">
+        <v>63.28848175999999</v>
+      </c>
+      <c r="P18">
+        <v>211.87883024</v>
+      </c>
+      <c r="Q18">
+        <v>241.07883024</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2470981273396361</v>
+      </c>
+      <c r="T18">
+        <v>1.215821355388072</v>
+      </c>
+      <c r="U18">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V18">
+        <v>0.23</v>
+      </c>
+      <c r="W18">
+        <v>0.04081000000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.026876741626204</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.213694319674991</v>
+      </c>
+      <c r="C19">
+        <v>7060.188519406367</v>
+      </c>
+      <c r="D19">
+        <v>8357.065519406367</v>
+      </c>
+      <c r="E19">
+        <v>884.3770000000002</v>
+      </c>
+      <c r="F19">
+        <v>1369.877</v>
+      </c>
+      <c r="G19">
+        <v>73</v>
+      </c>
+      <c r="H19">
+        <v>7572.6</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>372.7</v>
+      </c>
+      <c r="K19">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L19">
+        <v>343.5</v>
+      </c>
+      <c r="M19">
+        <v>72.60348100000002</v>
+      </c>
+      <c r="N19">
+        <v>270.896519</v>
+      </c>
+      <c r="O19">
+        <v>62.30619936999999</v>
+      </c>
+      <c r="P19">
+        <v>208.59031963</v>
+      </c>
+      <c r="Q19">
+        <v>237.79031963</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.249104361054206</v>
+      </c>
+      <c r="T19">
+        <v>1.22753159889927</v>
+      </c>
+      <c r="U19">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V19">
+        <v>0.23</v>
+      </c>
+      <c r="W19">
+        <v>0.04081000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>4.731178109765838</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.2132966123846877</v>
+      </c>
+      <c r="C20">
+        <v>6998.654685062986</v>
+      </c>
+      <c r="D20">
+        <v>8376.112685062986</v>
+      </c>
+      <c r="E20">
+        <v>964.9580000000001</v>
+      </c>
+      <c r="F20">
+        <v>1450.458</v>
+      </c>
+      <c r="G20">
+        <v>73</v>
+      </c>
+      <c r="H20">
+        <v>7572.6</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>372.7</v>
+      </c>
+      <c r="K20">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L20">
+        <v>343.5</v>
+      </c>
+      <c r="M20">
+        <v>76.87427400000001</v>
+      </c>
+      <c r="N20">
+        <v>266.625726</v>
+      </c>
+      <c r="O20">
+        <v>61.32391697999999</v>
+      </c>
+      <c r="P20">
+        <v>205.30180902</v>
+      </c>
+      <c r="Q20">
+        <v>234.50180902</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2511595272983996</v>
+      </c>
+      <c r="T20">
+        <v>1.239527458105863</v>
+      </c>
+      <c r="U20">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0.23</v>
+      </c>
+      <c r="W20">
+        <v>0.04081000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>4.468334881445513</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.2131915050943843</v>
+      </c>
+      <c r="C21">
+        <v>6923.122041673742</v>
+      </c>
+      <c r="D21">
+        <v>8381.161041673742</v>
+      </c>
+      <c r="E21">
+        <v>1045.539</v>
+      </c>
+      <c r="F21">
+        <v>1531.039</v>
+      </c>
+      <c r="G21">
+        <v>73</v>
+      </c>
+      <c r="H21">
+        <v>7572.6</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>372.7</v>
+      </c>
+      <c r="K21">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L21">
+        <v>343.5</v>
+      </c>
+      <c r="M21">
+        <v>84.207145</v>
+      </c>
+      <c r="N21">
+        <v>259.292855</v>
+      </c>
+      <c r="O21">
+        <v>59.63735665</v>
+      </c>
+      <c r="P21">
+        <v>199.65549835</v>
+      </c>
+      <c r="Q21">
+        <v>228.85549835</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.2532654383881288</v>
+      </c>
+      <c r="T21">
+        <v>1.251819511366939</v>
+      </c>
+      <c r="U21">
+        <v>0.055</v>
+      </c>
+      <c r="V21">
+        <v>0.23</v>
+      </c>
+      <c r="W21">
+        <v>0.04235</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>4.079226293683273</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.212809197804081</v>
+      </c>
+      <c r="C22">
+        <v>6860.954889952301</v>
+      </c>
+      <c r="D22">
+        <v>8399.574889952301</v>
+      </c>
+      <c r="E22">
+        <v>1126.12</v>
+      </c>
+      <c r="F22">
+        <v>1611.62</v>
+      </c>
+      <c r="G22">
+        <v>73</v>
+      </c>
+      <c r="H22">
+        <v>7572.6</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>372.7</v>
+      </c>
+      <c r="K22">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L22">
+        <v>343.5</v>
+      </c>
+      <c r="M22">
+        <v>88.63910000000001</v>
+      </c>
+      <c r="N22">
+        <v>254.8609</v>
+      </c>
+      <c r="O22">
+        <v>58.61800699999999</v>
+      </c>
+      <c r="P22">
+        <v>196.242893</v>
+      </c>
+      <c r="Q22">
+        <v>225.442893</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.2554239972551012</v>
+      </c>
+      <c r="T22">
+        <v>1.264418865959543</v>
+      </c>
+      <c r="U22">
+        <v>0.055</v>
+      </c>
+      <c r="V22">
+        <v>0.23</v>
+      </c>
+      <c r="W22">
+        <v>0.04235</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>3.875264978999109</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.2124268905137776</v>
+      </c>
+      <c r="C23">
+        <v>6798.868828762618</v>
+      </c>
+      <c r="D23">
+        <v>8418.069828762618</v>
+      </c>
+      <c r="E23">
+        <v>1206.701</v>
+      </c>
+      <c r="F23">
+        <v>1692.201</v>
+      </c>
+      <c r="G23">
+        <v>73</v>
+      </c>
+      <c r="H23">
+        <v>7572.6</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>372.7</v>
+      </c>
+      <c r="K23">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L23">
+        <v>343.5</v>
+      </c>
+      <c r="M23">
+        <v>93.071055</v>
+      </c>
+      <c r="N23">
+        <v>250.428945</v>
+      </c>
+      <c r="O23">
+        <v>57.59865735</v>
+      </c>
+      <c r="P23">
+        <v>192.83028765</v>
+      </c>
+      <c r="Q23">
+        <v>222.03028765</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.257637203181997</v>
+      </c>
+      <c r="T23">
+        <v>1.277337191554491</v>
+      </c>
+      <c r="U23">
+        <v>0.055</v>
+      </c>
+      <c r="V23">
+        <v>0.23</v>
+      </c>
+      <c r="W23">
+        <v>0.04235</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>3.690728551427723</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.2120445832234743</v>
+      </c>
+      <c r="C24">
+        <v>6736.864394944007</v>
+      </c>
+      <c r="D24">
+        <v>8436.646394944008</v>
+      </c>
+      <c r="E24">
+        <v>1287.282</v>
+      </c>
+      <c r="F24">
+        <v>1772.782</v>
+      </c>
+      <c r="G24">
+        <v>73</v>
+      </c>
+      <c r="H24">
+        <v>7572.6</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>372.7</v>
+      </c>
+      <c r="K24">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L24">
+        <v>343.5</v>
+      </c>
+      <c r="M24">
+        <v>97.50301</v>
+      </c>
+      <c r="N24">
+        <v>245.99699</v>
+      </c>
+      <c r="O24">
+        <v>56.57930769999999</v>
+      </c>
+      <c r="P24">
+        <v>189.4176823</v>
+      </c>
+      <c r="Q24">
+        <v>218.6176823</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.2599071579788132</v>
+      </c>
+      <c r="T24">
+        <v>1.290586756267258</v>
+      </c>
+      <c r="U24">
+        <v>0.055</v>
+      </c>
+      <c r="V24">
+        <v>0.23</v>
+      </c>
+      <c r="W24">
+        <v>0.04235</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>3.522968162726463</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.211662275933171</v>
+      </c>
+      <c r="C25">
+        <v>6674.942130084956</v>
+      </c>
+      <c r="D25">
+        <v>8455.305130084957</v>
+      </c>
+      <c r="E25">
+        <v>1367.863</v>
+      </c>
+      <c r="F25">
+        <v>1853.363</v>
+      </c>
+      <c r="G25">
+        <v>73</v>
+      </c>
+      <c r="H25">
+        <v>7572.6</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>372.7</v>
+      </c>
+      <c r="K25">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L25">
+        <v>343.5</v>
+      </c>
+      <c r="M25">
+        <v>101.934965</v>
+      </c>
+      <c r="N25">
+        <v>241.565035</v>
+      </c>
+      <c r="O25">
+        <v>55.55995804999999</v>
+      </c>
+      <c r="P25">
+        <v>186.00507695</v>
+      </c>
+      <c r="Q25">
+        <v>215.20507695</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.2622360726404818</v>
+      </c>
+      <c r="T25">
+        <v>1.304180465518019</v>
+      </c>
+      <c r="U25">
+        <v>0.055</v>
+      </c>
+      <c r="V25">
+        <v>0.23</v>
+      </c>
+      <c r="W25">
+        <v>0.04235</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>3.369795633912269</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.2112799686428676</v>
+      </c>
+      <c r="C26">
+        <v>6613.102580575734</v>
+      </c>
+      <c r="D26">
+        <v>8474.046580575734</v>
+      </c>
+      <c r="E26">
+        <v>1448.444</v>
+      </c>
+      <c r="F26">
+        <v>1933.944</v>
+      </c>
+      <c r="G26">
+        <v>73</v>
+      </c>
+      <c r="H26">
+        <v>7572.6</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>372.7</v>
+      </c>
+      <c r="K26">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L26">
+        <v>343.5</v>
+      </c>
+      <c r="M26">
+        <v>106.36692</v>
+      </c>
+      <c r="N26">
+        <v>237.13308</v>
+      </c>
+      <c r="O26">
+        <v>54.5406084</v>
+      </c>
+      <c r="P26">
+        <v>182.5924716</v>
+      </c>
+      <c r="Q26">
+        <v>211.7924716</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2646262745300889</v>
+      </c>
+      <c r="T26">
+        <v>1.31813190395959</v>
+      </c>
+      <c r="U26">
+        <v>0.055</v>
+      </c>
+      <c r="V26">
+        <v>0.23</v>
+      </c>
+      <c r="W26">
+        <v>0.04235</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>3.229387482499258</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.2108976613525642</v>
+      </c>
+      <c r="C27">
+        <v>6551.346297661734</v>
+      </c>
+      <c r="D27">
+        <v>8492.871297661733</v>
+      </c>
+      <c r="E27">
+        <v>1529.025</v>
+      </c>
+      <c r="F27">
+        <v>2014.525</v>
+      </c>
+      <c r="G27">
+        <v>73</v>
+      </c>
+      <c r="H27">
+        <v>7572.6</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>372.7</v>
+      </c>
+      <c r="K27">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L27">
+        <v>343.5</v>
+      </c>
+      <c r="M27">
+        <v>110.798875</v>
+      </c>
+      <c r="N27">
+        <v>232.701125</v>
+      </c>
+      <c r="O27">
+        <v>53.52125874999999</v>
+      </c>
+      <c r="P27">
+        <v>179.17986625</v>
+      </c>
+      <c r="Q27">
+        <v>208.37986625</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2670802151367523</v>
+      </c>
+      <c r="T27">
+        <v>1.332455380759602</v>
+      </c>
+      <c r="U27">
+        <v>0.055</v>
+      </c>
+      <c r="V27">
+        <v>0.23</v>
+      </c>
+      <c r="W27">
+        <v>0.04235</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>3.100211983199288</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.2112761140622609</v>
+      </c>
+      <c r="C28">
+        <v>6452.129962715904</v>
+      </c>
+      <c r="D28">
+        <v>8474.235962715904</v>
+      </c>
+      <c r="E28">
+        <v>1609.606</v>
+      </c>
+      <c r="F28">
+        <v>2095.106</v>
+      </c>
+      <c r="G28">
+        <v>73</v>
+      </c>
+      <c r="H28">
+        <v>7572.6</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>372.7</v>
+      </c>
+      <c r="K28">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L28">
+        <v>343.5</v>
+      </c>
+      <c r="M28">
+        <v>123.1922328</v>
+      </c>
+      <c r="N28">
+        <v>220.3077672</v>
+      </c>
+      <c r="O28">
+        <v>50.67078645599999</v>
+      </c>
+      <c r="P28">
+        <v>169.636980744</v>
+      </c>
+      <c r="Q28">
+        <v>198.836980744</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2696004784625148</v>
+      </c>
+      <c r="T28">
+        <v>1.34716597855421</v>
+      </c>
+      <c r="U28">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.23</v>
+      </c>
+      <c r="W28">
+        <v>0.045276</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>2.78832514187534</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.2109230667719576</v>
+      </c>
+      <c r="C29">
+        <v>6388.930747157332</v>
+      </c>
+      <c r="D29">
+        <v>8491.617747157332</v>
+      </c>
+      <c r="E29">
+        <v>1690.187</v>
+      </c>
+      <c r="F29">
+        <v>2175.687</v>
+      </c>
+      <c r="G29">
+        <v>73</v>
+      </c>
+      <c r="H29">
+        <v>7572.6</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>372.7</v>
+      </c>
+      <c r="K29">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L29">
+        <v>343.5</v>
+      </c>
+      <c r="M29">
+        <v>127.9303956</v>
+      </c>
+      <c r="N29">
+        <v>215.5696044</v>
+      </c>
+      <c r="O29">
+        <v>49.58100901199999</v>
+      </c>
+      <c r="P29">
+        <v>165.988595388</v>
+      </c>
+      <c r="Q29">
+        <v>195.188595388</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.272189790098572</v>
+      </c>
+      <c r="T29">
+        <v>1.362279606425382</v>
+      </c>
+      <c r="U29">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V29">
+        <v>0.23</v>
+      </c>
+      <c r="W29">
+        <v>0.045276</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>2.685053840324402</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2105700194816543</v>
+      </c>
+      <c r="C30">
+        <v>6325.802982855696</v>
+      </c>
+      <c r="D30">
+        <v>8509.070982855696</v>
+      </c>
+      <c r="E30">
+        <v>1770.768</v>
+      </c>
+      <c r="F30">
+        <v>2256.268</v>
+      </c>
+      <c r="G30">
+        <v>73</v>
+      </c>
+      <c r="H30">
+        <v>7572.6</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>372.7</v>
+      </c>
+      <c r="K30">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L30">
+        <v>343.5</v>
+      </c>
+      <c r="M30">
+        <v>132.6685584000001</v>
+      </c>
+      <c r="N30">
+        <v>210.8314415999999</v>
+      </c>
+      <c r="O30">
+        <v>48.49123156799998</v>
+      </c>
+      <c r="P30">
+        <v>162.340210032</v>
+      </c>
+      <c r="Q30">
+        <v>191.5402100319999</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2748510270578531</v>
+      </c>
+      <c r="T30">
+        <v>1.377813057292975</v>
+      </c>
+      <c r="U30">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V30">
+        <v>0.23</v>
+      </c>
+      <c r="W30">
+        <v>0.045276</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>2.589159060312816</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2111548321913509</v>
+      </c>
+      <c r="C31">
+        <v>6216.350074855112</v>
+      </c>
+      <c r="D31">
+        <v>8480.199074855112</v>
+      </c>
+      <c r="E31">
+        <v>1851.349</v>
+      </c>
+      <c r="F31">
+        <v>2336.849</v>
+      </c>
+      <c r="G31">
+        <v>73</v>
+      </c>
+      <c r="H31">
+        <v>7572.6</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>372.7</v>
+      </c>
+      <c r="K31">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L31">
+        <v>343.5</v>
+      </c>
+      <c r="M31">
+        <v>147.221487</v>
+      </c>
+      <c r="N31">
+        <v>196.278513</v>
+      </c>
+      <c r="O31">
+        <v>45.14405798999999</v>
+      </c>
+      <c r="P31">
+        <v>151.13445501</v>
+      </c>
+      <c r="Q31">
+        <v>180.33445501</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2775872284385224</v>
+      </c>
+      <c r="T31">
+        <v>1.393784070156839</v>
+      </c>
+      <c r="U31">
+        <v>0.063</v>
+      </c>
+      <c r="V31">
+        <v>0.23</v>
+      </c>
+      <c r="W31">
+        <v>0.04851</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>2.333219199178446</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2108341249010476</v>
+      </c>
+      <c r="C32">
+        <v>6151.577924803305</v>
+      </c>
+      <c r="D32">
+        <v>8496.007924803305</v>
+      </c>
+      <c r="E32">
+        <v>1931.93</v>
+      </c>
+      <c r="F32">
+        <v>2417.43</v>
+      </c>
+      <c r="G32">
+        <v>73</v>
+      </c>
+      <c r="H32">
+        <v>7572.6</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>372.7</v>
+      </c>
+      <c r="K32">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L32">
+        <v>343.5</v>
+      </c>
+      <c r="M32">
+        <v>152.29809</v>
+      </c>
+      <c r="N32">
+        <v>191.20191</v>
+      </c>
+      <c r="O32">
+        <v>43.9764393</v>
+      </c>
+      <c r="P32">
+        <v>147.2254707</v>
+      </c>
+      <c r="Q32">
+        <v>176.4254707</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2804016070014965</v>
+      </c>
+      <c r="T32">
+        <v>1.410211397673956</v>
+      </c>
+      <c r="U32">
+        <v>0.063</v>
+      </c>
+      <c r="V32">
+        <v>0.23</v>
+      </c>
+      <c r="W32">
+        <v>0.04851</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>2.255445225872498</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2172924976107442</v>
+      </c>
+      <c r="C33">
+        <v>5763.586885404466</v>
+      </c>
+      <c r="D33">
+        <v>8188.597885404467</v>
+      </c>
+      <c r="E33">
+        <v>2012.511</v>
+      </c>
+      <c r="F33">
+        <v>2498.011</v>
+      </c>
+      <c r="G33">
+        <v>73</v>
+      </c>
+      <c r="H33">
+        <v>7572.6</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>372.7</v>
+      </c>
+      <c r="K33">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L33">
+        <v>343.5</v>
+      </c>
+      <c r="M33">
+        <v>228.3182054</v>
+      </c>
+      <c r="N33">
+        <v>115.1817946</v>
+      </c>
+      <c r="O33">
+        <v>26.49181275799999</v>
+      </c>
+      <c r="P33">
+        <v>88.68998184199999</v>
+      </c>
+      <c r="Q33">
+        <v>117.889981842</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2832975617547018</v>
+      </c>
+      <c r="T33">
+        <v>1.427114879611859</v>
+      </c>
+      <c r="U33">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V33">
+        <v>0.23</v>
+      </c>
+      <c r="W33">
+        <v>0.07037800000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>1.504479239394021</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.236147251005569</v>
+      </c>
+      <c r="C34">
+        <v>4900.659067843131</v>
+      </c>
+      <c r="D34">
+        <v>7406.251067843131</v>
+      </c>
+      <c r="E34">
+        <v>2093.092</v>
+      </c>
+      <c r="F34">
+        <v>2578.592</v>
+      </c>
+      <c r="G34">
+        <v>73</v>
+      </c>
+      <c r="H34">
+        <v>7572.6</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>372.7</v>
+      </c>
+      <c r="K34">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L34">
+        <v>343.5</v>
+      </c>
+      <c r="M34">
+        <v>398.392464</v>
+      </c>
+      <c r="N34">
+        <v>-54.89246400000002</v>
+      </c>
+      <c r="O34">
+        <v>-12.62526672</v>
+      </c>
+      <c r="P34">
+        <v>-42.26719728000002</v>
+      </c>
+      <c r="Q34">
+        <v>-13.06719728000003</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.288987752062407</v>
+      </c>
+      <c r="T34">
+        <v>1.46032811575896</v>
+      </c>
+      <c r="U34">
+        <v>0.1545</v>
+      </c>
+      <c r="V34">
+        <v>0.1983094740466777</v>
+      </c>
+      <c r="W34">
+        <v>0.1238611862597883</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.8622151045507728</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.237304251005569</v>
+      </c>
+      <c r="C35">
+        <v>4776.910062915849</v>
+      </c>
+      <c r="D35">
+        <v>7363.08306291585</v>
+      </c>
+      <c r="E35">
+        <v>2173.673</v>
+      </c>
+      <c r="F35">
+        <v>2659.173</v>
+      </c>
+      <c r="G35">
+        <v>73</v>
+      </c>
+      <c r="H35">
+        <v>7572.6</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>372.7</v>
+      </c>
+      <c r="K35">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L35">
+        <v>343.5</v>
+      </c>
+      <c r="M35">
+        <v>410.8422285</v>
+      </c>
+      <c r="N35">
+        <v>-67.34222850000003</v>
+      </c>
+      <c r="O35">
+        <v>-15.48871255500001</v>
+      </c>
+      <c r="P35">
+        <v>-51.85351594500003</v>
+      </c>
+      <c r="Q35">
+        <v>-22.65351594500004</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2927218976155773</v>
+      </c>
+      <c r="T35">
+        <v>1.482124057785213</v>
+      </c>
+      <c r="U35">
+        <v>0.1545</v>
+      </c>
+      <c r="V35">
+        <v>0.1923000960452632</v>
+      </c>
+      <c r="W35">
+        <v>0.1247896351610068</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.8360873741098402</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.238461251005569</v>
+      </c>
+      <c r="C36">
+        <v>4653.66135918822</v>
+      </c>
+      <c r="D36">
+        <v>7320.41535918822</v>
+      </c>
+      <c r="E36">
+        <v>2254.254</v>
+      </c>
+      <c r="F36">
+        <v>2739.754</v>
+      </c>
+      <c r="G36">
+        <v>73</v>
+      </c>
+      <c r="H36">
+        <v>7572.6</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>372.7</v>
+      </c>
+      <c r="K36">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L36">
+        <v>343.5</v>
+      </c>
+      <c r="M36">
+        <v>423.291993</v>
+      </c>
+      <c r="N36">
+        <v>-79.79199300000005</v>
+      </c>
+      <c r="O36">
+        <v>-18.35215839000001</v>
+      </c>
+      <c r="P36">
+        <v>-61.43983461000003</v>
+      </c>
+      <c r="Q36">
+        <v>-32.23983461000005</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2965691990946012</v>
+      </c>
+      <c r="T36">
+        <v>1.504580482903171</v>
+      </c>
+      <c r="U36">
+        <v>0.1545</v>
+      </c>
+      <c r="V36">
+        <v>0.1866442108674614</v>
+      </c>
+      <c r="W36">
+        <v>0.1256634694209772</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.8114965689889626</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2635705894616834</v>
+      </c>
+      <c r="C37">
+        <v>3755.309727659359</v>
+      </c>
+      <c r="D37">
+        <v>6502.64472765936</v>
+      </c>
+      <c r="E37">
+        <v>2334.835</v>
+      </c>
+      <c r="F37">
+        <v>2820.335</v>
+      </c>
+      <c r="G37">
+        <v>73</v>
+      </c>
+      <c r="H37">
+        <v>7572.6</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>372.7</v>
+      </c>
+      <c r="K37">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L37">
+        <v>343.5</v>
+      </c>
+      <c r="M37">
+        <v>602.9876230000001</v>
+      </c>
+      <c r="N37">
+        <v>-259.4876230000001</v>
+      </c>
+      <c r="O37">
+        <v>-59.68215329000002</v>
+      </c>
+      <c r="P37">
+        <v>-199.8054697100001</v>
+      </c>
+      <c r="Q37">
+        <v>-170.6054697100001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.305453861320848</v>
+      </c>
+      <c r="T37">
+        <v>1.556439624452088</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.1310225898285146</v>
+      </c>
+      <c r="W37">
+        <v>0.1857873702946636</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.5696634340370199</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2653205894616834</v>
+      </c>
+      <c r="C38">
+        <v>3624.492109873545</v>
+      </c>
+      <c r="D38">
+        <v>6452.408109873545</v>
+      </c>
+      <c r="E38">
+        <v>2415.416</v>
+      </c>
+      <c r="F38">
+        <v>2900.916</v>
+      </c>
+      <c r="G38">
+        <v>73</v>
+      </c>
+      <c r="H38">
+        <v>7572.6</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>372.7</v>
+      </c>
+      <c r="K38">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L38">
+        <v>343.5</v>
+      </c>
+      <c r="M38">
+        <v>620.2158408</v>
+      </c>
+      <c r="N38">
+        <v>-276.7158408</v>
+      </c>
+      <c r="O38">
+        <v>-63.644643384</v>
+      </c>
+      <c r="P38">
+        <v>-213.071197416</v>
+      </c>
+      <c r="Q38">
+        <v>-183.871197416</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.3096203279039862</v>
+      </c>
+      <c r="T38">
+        <v>1.580758993584152</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.1273830734443892</v>
+      </c>
+      <c r="W38">
+        <v>0.1865654988975896</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.553839449758214</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2670705894616834</v>
+      </c>
+      <c r="C39">
+        <v>3494.444754094171</v>
+      </c>
+      <c r="D39">
+        <v>6402.941754094171</v>
+      </c>
+      <c r="E39">
+        <v>2495.997</v>
+      </c>
+      <c r="F39">
+        <v>2981.497</v>
+      </c>
+      <c r="G39">
+        <v>73</v>
+      </c>
+      <c r="H39">
+        <v>7572.6</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>372.7</v>
+      </c>
+      <c r="K39">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L39">
+        <v>343.5</v>
+      </c>
+      <c r="M39">
+        <v>637.4440586000001</v>
+      </c>
+      <c r="N39">
+        <v>-293.9440586000001</v>
+      </c>
+      <c r="O39">
+        <v>-67.60713347800001</v>
+      </c>
+      <c r="P39">
+        <v>-226.3369251220001</v>
+      </c>
+      <c r="Q39">
+        <v>-197.1369251220001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.3139190632675415</v>
+      </c>
+      <c r="T39">
+        <v>1.605850406180726</v>
+      </c>
+      <c r="U39">
+        <v>0.2138</v>
+      </c>
+      <c r="V39">
+        <v>0.1239402876756219</v>
+      </c>
+      <c r="W39">
+        <v>0.187301566494952</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.5388708159809648</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2688205894616834</v>
+      </c>
+      <c r="C40">
+        <v>3365.150079827498</v>
+      </c>
+      <c r="D40">
+        <v>6354.228079827498</v>
+      </c>
+      <c r="E40">
+        <v>2576.578</v>
+      </c>
+      <c r="F40">
+        <v>3062.078</v>
+      </c>
+      <c r="G40">
+        <v>73</v>
+      </c>
+      <c r="H40">
+        <v>7572.6</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>372.7</v>
+      </c>
+      <c r="K40">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L40">
+        <v>343.5</v>
+      </c>
+      <c r="M40">
+        <v>654.6722764</v>
+      </c>
+      <c r="N40">
+        <v>-311.1722764</v>
+      </c>
+      <c r="O40">
+        <v>-71.569623572</v>
+      </c>
+      <c r="P40">
+        <v>-239.602652828</v>
+      </c>
+      <c r="Q40">
+        <v>-210.402652828</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.3183564675137922</v>
+      </c>
+      <c r="T40">
+        <v>1.631751219183641</v>
+      </c>
+      <c r="U40">
+        <v>0.2138</v>
+      </c>
+      <c r="V40">
+        <v>0.1206787011578424</v>
+      </c>
+      <c r="W40">
+        <v>0.1879988936924533</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.5246900050340975</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2705705894616834</v>
+      </c>
+      <c r="C41">
+        <v>3236.591037550754</v>
+      </c>
+      <c r="D41">
+        <v>6306.250037550754</v>
+      </c>
+      <c r="E41">
+        <v>2657.159</v>
+      </c>
+      <c r="F41">
+        <v>3142.659</v>
+      </c>
+      <c r="G41">
+        <v>73</v>
+      </c>
+      <c r="H41">
+        <v>7572.6</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>372.7</v>
+      </c>
+      <c r="K41">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L41">
+        <v>343.5</v>
+      </c>
+      <c r="M41">
+        <v>671.9004942</v>
+      </c>
+      <c r="N41">
+        <v>-328.4004942</v>
+      </c>
+      <c r="O41">
+        <v>-75.532113666</v>
+      </c>
+      <c r="P41">
+        <v>-252.868380534</v>
+      </c>
+      <c r="Q41">
+        <v>-223.6683805340001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.3229393604238544</v>
+      </c>
+      <c r="T41">
+        <v>1.658501239170258</v>
+      </c>
+      <c r="U41">
+        <v>0.2138</v>
+      </c>
+      <c r="V41">
+        <v>0.1175843754871285</v>
+      </c>
+      <c r="W41">
+        <v>0.1886604605208519</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.5112364151614281</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2723205894616835</v>
+      </c>
+      <c r="C42">
+        <v>3108.751088816708</v>
+      </c>
+      <c r="D42">
+        <v>6258.991088816709</v>
+      </c>
+      <c r="E42">
+        <v>2737.74</v>
+      </c>
+      <c r="F42">
+        <v>3223.24</v>
+      </c>
+      <c r="G42">
+        <v>73</v>
+      </c>
+      <c r="H42">
+        <v>7572.6</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>372.7</v>
+      </c>
+      <c r="K42">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L42">
+        <v>343.5</v>
+      </c>
+      <c r="M42">
+        <v>689.1287120000001</v>
+      </c>
+      <c r="N42">
+        <v>-345.6287120000001</v>
+      </c>
+      <c r="O42">
+        <v>-79.49460376</v>
+      </c>
+      <c r="P42">
+        <v>-266.13410824</v>
+      </c>
+      <c r="Q42">
+        <v>-236.9341082400001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.3276750164309187</v>
+      </c>
+      <c r="T42">
+        <v>1.686142926489762</v>
+      </c>
+      <c r="U42">
+        <v>0.2138</v>
+      </c>
+      <c r="V42">
+        <v>0.1146447660999503</v>
+      </c>
+      <c r="W42">
+        <v>0.1892889490078306</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.4984555047823924</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2740705894616834</v>
+      </c>
+      <c r="C43">
+        <v>2981.614187246135</v>
+      </c>
+      <c r="D43">
+        <v>6212.435187246136</v>
+      </c>
+      <c r="E43">
+        <v>2818.321</v>
+      </c>
+      <c r="F43">
+        <v>3303.821</v>
+      </c>
+      <c r="G43">
+        <v>73</v>
+      </c>
+      <c r="H43">
+        <v>7572.6</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>372.7</v>
+      </c>
+      <c r="K43">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L43">
+        <v>343.5</v>
+      </c>
+      <c r="M43">
+        <v>706.3569298</v>
+      </c>
+      <c r="N43">
+        <v>-362.8569298</v>
+      </c>
+      <c r="O43">
+        <v>-83.45709385399999</v>
+      </c>
+      <c r="P43">
+        <v>-279.399835946</v>
+      </c>
+      <c r="Q43">
+        <v>-250.199835946</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.3325712031500868</v>
+      </c>
+      <c r="T43">
+        <v>1.71472162015908</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.1118485522926344</v>
+      </c>
+      <c r="W43">
+        <v>0.1898867795198347</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.4862980534462367</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2758205894616834</v>
+      </c>
+      <c r="C44">
+        <v>2855.164760362325</v>
+      </c>
+      <c r="D44">
+        <v>6166.566760362325</v>
+      </c>
+      <c r="E44">
+        <v>2898.902</v>
+      </c>
+      <c r="F44">
+        <v>3384.402</v>
+      </c>
+      <c r="G44">
+        <v>73</v>
+      </c>
+      <c r="H44">
+        <v>7572.6</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>372.7</v>
+      </c>
+      <c r="K44">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L44">
+        <v>343.5</v>
+      </c>
+      <c r="M44">
+        <v>723.5851476</v>
+      </c>
+      <c r="N44">
+        <v>-380.0851476</v>
+      </c>
+      <c r="O44">
+        <v>-87.419583948</v>
+      </c>
+      <c r="P44">
+        <v>-292.6655636520001</v>
+      </c>
+      <c r="Q44">
+        <v>-263.4655636520001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.3376362238940537</v>
+      </c>
+      <c r="T44">
+        <v>1.744285786023892</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.1091854915237622</v>
+      </c>
+      <c r="W44">
+        <v>0.1904561419122196</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.4747195283641833</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2775705894616834</v>
+      </c>
+      <c r="C45">
+        <v>2729.387692224435</v>
+      </c>
+      <c r="D45">
+        <v>6121.370692224436</v>
+      </c>
+      <c r="E45">
+        <v>2979.483</v>
+      </c>
+      <c r="F45">
+        <v>3464.983</v>
+      </c>
+      <c r="G45">
+        <v>73</v>
+      </c>
+      <c r="H45">
+        <v>7572.6</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>372.7</v>
+      </c>
+      <c r="K45">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L45">
+        <v>343.5</v>
+      </c>
+      <c r="M45">
+        <v>740.8133654</v>
+      </c>
+      <c r="N45">
+        <v>-397.3133654</v>
+      </c>
+      <c r="O45">
+        <v>-91.38207404199999</v>
+      </c>
+      <c r="P45">
+        <v>-305.931291358</v>
+      </c>
+      <c r="Q45">
+        <v>-276.731291358</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.3428789646641248</v>
+      </c>
+      <c r="T45">
+        <v>1.774887291041854</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.1066462940464654</v>
+      </c>
+      <c r="W45">
+        <v>0.1909990223328657</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.4636795393324582</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2793205894616835</v>
+      </c>
+      <c r="C46">
+        <v>2604.268306818975</v>
+      </c>
+      <c r="D46">
+        <v>6076.832306818976</v>
+      </c>
+      <c r="E46">
+        <v>3060.064</v>
+      </c>
+      <c r="F46">
+        <v>3545.564</v>
+      </c>
+      <c r="G46">
+        <v>73</v>
+      </c>
+      <c r="H46">
+        <v>7572.6</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>372.7</v>
+      </c>
+      <c r="K46">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L46">
+        <v>343.5</v>
+      </c>
+      <c r="M46">
+        <v>758.0415832</v>
+      </c>
+      <c r="N46">
+        <v>-414.5415832</v>
+      </c>
+      <c r="O46">
+        <v>-95.34456413599999</v>
+      </c>
+      <c r="P46">
+        <v>-319.197019064</v>
+      </c>
+      <c r="Q46">
+        <v>-289.997019064</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.3483089461759842</v>
+      </c>
+      <c r="T46">
+        <v>1.806581706953316</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.1042225146363184</v>
+      </c>
+      <c r="W46">
+        <v>0.1915172263707551</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.4531413679839932</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2810705894616835</v>
+      </c>
+      <c r="C47">
+        <v>2479.792352171106</v>
+      </c>
+      <c r="D47">
+        <v>6032.937352171107</v>
+      </c>
+      <c r="E47">
+        <v>3140.645</v>
+      </c>
+      <c r="F47">
+        <v>3626.145</v>
+      </c>
+      <c r="G47">
+        <v>73</v>
+      </c>
+      <c r="H47">
+        <v>7572.6</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>372.7</v>
+      </c>
+      <c r="K47">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L47">
+        <v>343.5</v>
+      </c>
+      <c r="M47">
+        <v>775.269801</v>
+      </c>
+      <c r="N47">
+        <v>-431.769801</v>
+      </c>
+      <c r="O47">
+        <v>-99.30705423000001</v>
+      </c>
+      <c r="P47">
+        <v>-332.46274677</v>
+      </c>
+      <c r="Q47">
+        <v>-303.26274677</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.3539363815610022</v>
+      </c>
+      <c r="T47">
+        <v>1.83942864707974</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.1019064587555113</v>
+      </c>
+      <c r="W47">
+        <v>0.1920123991180717</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.4430715598065711</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2828205894616834</v>
+      </c>
+      <c r="C48">
+        <v>2355.945985139621</v>
+      </c>
+      <c r="D48">
+        <v>5989.671985139621</v>
+      </c>
+      <c r="E48">
+        <v>3221.226</v>
+      </c>
+      <c r="F48">
+        <v>3706.726</v>
+      </c>
+      <c r="G48">
+        <v>73</v>
+      </c>
+      <c r="H48">
+        <v>7572.6</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>372.7</v>
+      </c>
+      <c r="K48">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L48">
+        <v>343.5</v>
+      </c>
+      <c r="M48">
+        <v>792.4980188</v>
+      </c>
+      <c r="N48">
+        <v>-448.9980188</v>
+      </c>
+      <c r="O48">
+        <v>-103.269544324</v>
+      </c>
+      <c r="P48">
+        <v>-345.728474476</v>
+      </c>
+      <c r="Q48">
+        <v>-316.528474476</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.3597722404787985</v>
+      </c>
+      <c r="T48">
+        <v>1.87349214054418</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.09969110095647851</v>
+      </c>
+      <c r="W48">
+        <v>0.1924860426155049</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.4334395693759935</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2845705894616835</v>
+      </c>
+      <c r="C49">
+        <v>2232.715756861521</v>
+      </c>
+      <c r="D49">
+        <v>5947.022756861521</v>
+      </c>
+      <c r="E49">
+        <v>3301.807</v>
+      </c>
+      <c r="F49">
+        <v>3787.307</v>
+      </c>
+      <c r="G49">
+        <v>73</v>
+      </c>
+      <c r="H49">
+        <v>7572.6</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>372.7</v>
+      </c>
+      <c r="K49">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L49">
+        <v>343.5</v>
+      </c>
+      <c r="M49">
+        <v>809.7262366</v>
+      </c>
+      <c r="N49">
+        <v>-466.2262366</v>
+      </c>
+      <c r="O49">
+        <v>-107.232034418</v>
+      </c>
+      <c r="P49">
+        <v>-358.994202182</v>
+      </c>
+      <c r="Q49">
+        <v>-329.794202182</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.3658283204878324</v>
+      </c>
+      <c r="T49">
+        <v>1.908841048856334</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.09757001370208535</v>
+      </c>
+      <c r="W49">
+        <v>0.1929395310704941</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.4242174508786319</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2863205894616834</v>
+      </c>
+      <c r="C50">
+        <v>2110.088598814057</v>
+      </c>
+      <c r="D50">
+        <v>5904.976598814057</v>
+      </c>
+      <c r="E50">
+        <v>3382.388</v>
+      </c>
+      <c r="F50">
+        <v>3867.888</v>
+      </c>
+      <c r="G50">
+        <v>73</v>
+      </c>
+      <c r="H50">
+        <v>7572.6</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>372.7</v>
+      </c>
+      <c r="K50">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L50">
+        <v>343.5</v>
+      </c>
+      <c r="M50">
+        <v>826.9544543999999</v>
+      </c>
+      <c r="N50">
+        <v>-483.4544543999999</v>
+      </c>
+      <c r="O50">
+        <v>-111.194524512</v>
+      </c>
+      <c r="P50">
+        <v>-372.2599298879999</v>
+      </c>
+      <c r="Q50">
+        <v>-343.0599298879999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.37211732665106</v>
+      </c>
+      <c r="T50">
+        <v>1.94554953056511</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.0955373050832919</v>
+      </c>
+      <c r="W50">
+        <v>0.1933741241731922</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.4153795873186604</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2880705894616834</v>
+      </c>
+      <c r="C51">
+        <v>1988.051809463854</v>
+      </c>
+      <c r="D51">
+        <v>5863.520809463854</v>
+      </c>
+      <c r="E51">
+        <v>3462.969</v>
+      </c>
+      <c r="F51">
+        <v>3948.469</v>
+      </c>
+      <c r="G51">
+        <v>73</v>
+      </c>
+      <c r="H51">
+        <v>7572.6</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>372.7</v>
+      </c>
+      <c r="K51">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L51">
+        <v>343.5</v>
+      </c>
+      <c r="M51">
+        <v>844.1826722</v>
+      </c>
+      <c r="N51">
+        <v>-500.6826722</v>
+      </c>
+      <c r="O51">
+        <v>-115.157014606</v>
+      </c>
+      <c r="P51">
+        <v>-385.525657594</v>
+      </c>
+      <c r="Q51">
+        <v>-356.325657594</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.3786529605069631</v>
+      </c>
+      <c r="T51">
+        <v>1.98369756057619</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0.09358756416322471</v>
+      </c>
+      <c r="W51">
+        <v>0.1937909787819025</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.4069024528835857</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2898205894616834</v>
+      </c>
+      <c r="C52">
+        <v>1866.593041474513</v>
+      </c>
+      <c r="D52">
+        <v>5822.643041474514</v>
+      </c>
+      <c r="E52">
+        <v>3543.55</v>
+      </c>
+      <c r="F52">
+        <v>4029.05</v>
+      </c>
+      <c r="G52">
+        <v>73</v>
+      </c>
+      <c r="H52">
+        <v>7572.6</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>372.7</v>
+      </c>
+      <c r="K52">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L52">
+        <v>343.5</v>
+      </c>
+      <c r="M52">
+        <v>861.41089</v>
+      </c>
+      <c r="N52">
+        <v>-517.91089</v>
+      </c>
+      <c r="O52">
+        <v>-119.1195047</v>
+      </c>
+      <c r="P52">
+        <v>-398.7913853</v>
+      </c>
+      <c r="Q52">
+        <v>-369.5913853</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.3854500197171024</v>
+      </c>
+      <c r="T52">
+        <v>2.023371511787714</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.09171581287996022</v>
+      </c>
+      <c r="W52">
+        <v>0.1941911592062645</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.398764403825914</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2915705894616834</v>
+      </c>
+      <c r="C53">
+        <v>1745.700289445606</v>
+      </c>
+      <c r="D53">
+        <v>5782.331289445607</v>
+      </c>
+      <c r="E53">
+        <v>3624.131</v>
+      </c>
+      <c r="F53">
+        <v>4109.631</v>
+      </c>
+      <c r="G53">
+        <v>73</v>
+      </c>
+      <c r="H53">
+        <v>7572.6</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>372.7</v>
+      </c>
+      <c r="K53">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L53">
+        <v>343.5</v>
+      </c>
+      <c r="M53">
+        <v>878.6391078</v>
+      </c>
+      <c r="N53">
+        <v>-535.1391078</v>
+      </c>
+      <c r="O53">
+        <v>-123.081994794</v>
+      </c>
+      <c r="P53">
+        <v>-412.057113006</v>
+      </c>
+      <c r="Q53">
+        <v>-382.857113006</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.3925245099154105</v>
+      </c>
+      <c r="T53">
+        <v>2.064664807946647</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0.08991746360780413</v>
+      </c>
+      <c r="W53">
+        <v>0.1945756462806515</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3909454939469745</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2933205894616835</v>
+      </c>
+      <c r="C54">
+        <v>1625.361878157457</v>
+      </c>
+      <c r="D54">
+        <v>5742.573878157457</v>
+      </c>
+      <c r="E54">
+        <v>3704.712</v>
+      </c>
+      <c r="F54">
+        <v>4190.212</v>
+      </c>
+      <c r="G54">
+        <v>73</v>
+      </c>
+      <c r="H54">
+        <v>7572.6</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>372.7</v>
+      </c>
+      <c r="K54">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L54">
+        <v>343.5</v>
+      </c>
+      <c r="M54">
+        <v>895.8673256000001</v>
+      </c>
+      <c r="N54">
+        <v>-552.3673256000001</v>
+      </c>
+      <c r="O54">
+        <v>-127.044484888</v>
+      </c>
+      <c r="P54">
+        <v>-425.3228407120001</v>
+      </c>
+      <c r="Q54">
+        <v>-396.1228407120001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.3998937705386484</v>
+      </c>
+      <c r="T54">
+        <v>2.107678658112203</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0.08818828161534636</v>
+      </c>
+      <c r="W54">
+        <v>0.194945345390639</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3834273113710711</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2950705894616834</v>
+      </c>
+      <c r="C55">
+        <v>1505.56645129761</v>
+      </c>
+      <c r="D55">
+        <v>5703.359451297611</v>
+      </c>
+      <c r="E55">
+        <v>3785.293000000001</v>
+      </c>
+      <c r="F55">
+        <v>4270.793000000001</v>
+      </c>
+      <c r="G55">
+        <v>73</v>
+      </c>
+      <c r="H55">
+        <v>7572.6</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>372.7</v>
+      </c>
+      <c r="K55">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L55">
+        <v>343.5</v>
+      </c>
+      <c r="M55">
+        <v>913.0955434000001</v>
+      </c>
+      <c r="N55">
+        <v>-569.5955434000001</v>
+      </c>
+      <c r="O55">
+        <v>-131.006974982</v>
+      </c>
+      <c r="P55">
+        <v>-438.5885684180001</v>
+      </c>
+      <c r="Q55">
+        <v>-409.3885684180001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.4075766167203217</v>
+      </c>
+      <c r="T55">
+        <v>2.152522884880547</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0.08652435177354736</v>
+      </c>
+      <c r="W55">
+        <v>0.1953010935908156</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.376192833798032</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2968205894616834</v>
+      </c>
+      <c r="C56">
+        <v>1386.302960646013</v>
+      </c>
+      <c r="D56">
+        <v>5664.676960646014</v>
+      </c>
+      <c r="E56">
+        <v>3865.874000000001</v>
+      </c>
+      <c r="F56">
+        <v>4351.374000000001</v>
+      </c>
+      <c r="G56">
+        <v>73</v>
+      </c>
+      <c r="H56">
+        <v>7572.6</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>372.7</v>
+      </c>
+      <c r="K56">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L56">
+        <v>343.5</v>
+      </c>
+      <c r="M56">
+        <v>930.3237612000001</v>
+      </c>
+      <c r="N56">
+        <v>-586.8237612000001</v>
+      </c>
+      <c r="O56">
+        <v>-134.969465076</v>
+      </c>
+      <c r="P56">
+        <v>-451.8542961240001</v>
+      </c>
+      <c r="Q56">
+        <v>-422.6542961240002</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.4155934996925025</v>
+      </c>
+      <c r="T56">
+        <v>2.19931686063882</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0.08492204896292611</v>
+      </c>
+      <c r="W56">
+        <v>0.1956436659317264</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3692262998388092</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2985705894616834</v>
+      </c>
+      <c r="C57">
+        <v>1267.560655697392</v>
+      </c>
+      <c r="D57">
+        <v>5626.515655697393</v>
+      </c>
+      <c r="E57">
+        <v>3946.455000000001</v>
+      </c>
+      <c r="F57">
+        <v>4431.955000000001</v>
+      </c>
+      <c r="G57">
+        <v>73</v>
+      </c>
+      <c r="H57">
+        <v>7572.6</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>372.7</v>
+      </c>
+      <c r="K57">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L57">
+        <v>343.5</v>
+      </c>
+      <c r="M57">
+        <v>947.5519790000002</v>
+      </c>
+      <c r="N57">
+        <v>-604.0519790000002</v>
+      </c>
+      <c r="O57">
+        <v>-138.93195517</v>
+      </c>
+      <c r="P57">
+        <v>-465.1200238300002</v>
+      </c>
+      <c r="Q57">
+        <v>-435.9200238300002</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.4239666885745582</v>
+      </c>
+      <c r="T57">
+        <v>2.248190568653016</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.08337801170905472</v>
+      </c>
+      <c r="W57">
+        <v>0.1959737810966041</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.3625130943871945</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.3003205894616834</v>
+      </c>
+      <c r="C58">
+        <v>1149.32907370024</v>
+      </c>
+      <c r="D58">
+        <v>5588.865073700241</v>
+      </c>
+      <c r="E58">
+        <v>4027.036000000001</v>
+      </c>
+      <c r="F58">
+        <v>4512.536000000001</v>
+      </c>
+      <c r="G58">
+        <v>73</v>
+      </c>
+      <c r="H58">
+        <v>7572.6</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>372.7</v>
+      </c>
+      <c r="K58">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L58">
+        <v>343.5</v>
+      </c>
+      <c r="M58">
+        <v>964.7801968000001</v>
+      </c>
+      <c r="N58">
+        <v>-621.2801968000001</v>
+      </c>
+      <c r="O58">
+        <v>-142.894445264</v>
+      </c>
+      <c r="P58">
+        <v>-478.3857515360001</v>
+      </c>
+      <c r="Q58">
+        <v>-449.1857515360001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.4327204769512527</v>
+      </c>
+      <c r="T58">
+        <v>2.299285808849675</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.08188911864282161</v>
+      </c>
+      <c r="W58">
+        <v>0.1962921064341647</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3560396462731374</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.3020705894616834</v>
+      </c>
+      <c r="C59">
+        <v>1031.598030093114</v>
+      </c>
+      <c r="D59">
+        <v>5551.715030093115</v>
+      </c>
+      <c r="E59">
+        <v>4107.617000000001</v>
+      </c>
+      <c r="F59">
+        <v>4593.117000000001</v>
+      </c>
+      <c r="G59">
+        <v>73</v>
+      </c>
+      <c r="H59">
+        <v>7572.6</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>372.7</v>
+      </c>
+      <c r="K59">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L59">
+        <v>343.5</v>
+      </c>
+      <c r="M59">
+        <v>982.0084146000002</v>
+      </c>
+      <c r="N59">
+        <v>-638.5084146000002</v>
+      </c>
+      <c r="O59">
+        <v>-146.856935358</v>
+      </c>
+      <c r="P59">
+        <v>-491.6514792420002</v>
+      </c>
+      <c r="Q59">
+        <v>-462.4514792420002</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.4418814182757004</v>
+      </c>
+      <c r="T59">
+        <v>2.352757571846179</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.08045246743856159</v>
+      </c>
+      <c r="W59">
+        <v>0.1965992624616355</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.3497933366893982</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.3038205894616834</v>
+      </c>
+      <c r="C60">
+        <v>914.357609319818</v>
+      </c>
+      <c r="D60">
+        <v>5515.055609319818</v>
+      </c>
+      <c r="E60">
+        <v>4188.198</v>
+      </c>
+      <c r="F60">
+        <v>4673.698</v>
+      </c>
+      <c r="G60">
+        <v>73</v>
+      </c>
+      <c r="H60">
+        <v>7572.6</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>372.7</v>
+      </c>
+      <c r="K60">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L60">
+        <v>343.5</v>
+      </c>
+      <c r="M60">
+        <v>999.2366324000001</v>
+      </c>
+      <c r="N60">
+        <v>-655.7366324000001</v>
+      </c>
+      <c r="O60">
+        <v>-150.819425452</v>
+      </c>
+      <c r="P60">
+        <v>-504.9172069480001</v>
+      </c>
+      <c r="Q60">
+        <v>-475.7172069480001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.4514785949013122</v>
+      </c>
+      <c r="T60">
+        <v>2.408775609271088</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.07906535593100018</v>
+      </c>
+      <c r="W60">
+        <v>0.1968958269019521</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.3437624170913052</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.3055705894616834</v>
+      </c>
+      <c r="C61">
+        <v>797.5981560061109</v>
+      </c>
+      <c r="D61">
+        <v>5478.87715600611</v>
+      </c>
+      <c r="E61">
+        <v>4268.779</v>
+      </c>
+      <c r="F61">
+        <v>4754.279</v>
+      </c>
+      <c r="G61">
+        <v>73</v>
+      </c>
+      <c r="H61">
+        <v>7572.6</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>372.7</v>
+      </c>
+      <c r="K61">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L61">
+        <v>343.5</v>
+      </c>
+      <c r="M61">
+        <v>1016.4648502</v>
+      </c>
+      <c r="N61">
+        <v>-672.9648501999999</v>
+      </c>
+      <c r="O61">
+        <v>-154.781915546</v>
+      </c>
+      <c r="P61">
+        <v>-518.182934654</v>
+      </c>
+      <c r="Q61">
+        <v>-488.982934654</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.4615439264842712</v>
+      </c>
+      <c r="T61">
+        <v>2.467526233887456</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.07772526515250867</v>
+      </c>
+      <c r="W61">
+        <v>0.1971823383103936</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3379359354456899</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.3073205894616834</v>
+      </c>
+      <c r="C62">
+        <v>681.3102664814305</v>
+      </c>
+      <c r="D62">
+        <v>5443.17026648143</v>
+      </c>
+      <c r="E62">
+        <v>4349.36</v>
+      </c>
+      <c r="F62">
+        <v>4834.86</v>
+      </c>
+      <c r="G62">
+        <v>73</v>
+      </c>
+      <c r="H62">
+        <v>7572.6</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>372.7</v>
+      </c>
+      <c r="K62">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L62">
+        <v>343.5</v>
+      </c>
+      <c r="M62">
+        <v>1033.693068</v>
+      </c>
+      <c r="N62">
+        <v>-690.1930679999998</v>
+      </c>
+      <c r="O62">
+        <v>-158.7444056399999</v>
+      </c>
+      <c r="P62">
+        <v>-531.4486623599998</v>
+      </c>
+      <c r="Q62">
+        <v>-502.2486623599999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.4721125246463779</v>
+      </c>
+      <c r="T62">
+        <v>2.529214389734642</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.07642984406663353</v>
+      </c>
+      <c r="W62">
+        <v>0.1974592993385537</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3323036698549284</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.3090705894616834</v>
+      </c>
+      <c r="C63">
+        <v>565.4847806299904</v>
+      </c>
+      <c r="D63">
+        <v>5407.92578062999</v>
+      </c>
+      <c r="E63">
+        <v>4429.941</v>
+      </c>
+      <c r="F63">
+        <v>4915.441</v>
+      </c>
+      <c r="G63">
+        <v>73</v>
+      </c>
+      <c r="H63">
+        <v>7572.6</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>372.7</v>
+      </c>
+      <c r="K63">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L63">
+        <v>343.5</v>
+      </c>
+      <c r="M63">
+        <v>1050.9212858</v>
+      </c>
+      <c r="N63">
+        <v>-707.4212857999999</v>
+      </c>
+      <c r="O63">
+        <v>-162.7068957339999</v>
+      </c>
+      <c r="P63">
+        <v>-544.7143900659999</v>
+      </c>
+      <c r="Q63">
+        <v>-515.5143900659998</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.4832231022014133</v>
+      </c>
+      <c r="T63">
+        <v>2.59406604075348</v>
+      </c>
+      <c r="U63">
+        <v>0.2138</v>
+      </c>
+      <c r="V63">
+        <v>0.07517689580324609</v>
+      </c>
+      <c r="W63">
+        <v>0.197727179677266</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.3268560687097657</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.3108205894616834</v>
+      </c>
+      <c r="C64">
+        <v>450.1127740564398</v>
+      </c>
+      <c r="D64">
+        <v>5373.13477405644</v>
+      </c>
+      <c r="E64">
+        <v>4510.522</v>
+      </c>
+      <c r="F64">
+        <v>4996.022</v>
+      </c>
+      <c r="G64">
+        <v>73</v>
+      </c>
+      <c r="H64">
+        <v>7572.6</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>372.7</v>
+      </c>
+      <c r="K64">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L64">
+        <v>343.5</v>
+      </c>
+      <c r="M64">
+        <v>1068.1495036</v>
+      </c>
+      <c r="N64">
+        <v>-724.6495035999999</v>
+      </c>
+      <c r="O64">
+        <v>-166.669385828</v>
+      </c>
+      <c r="P64">
+        <v>-557.9801177719999</v>
+      </c>
+      <c r="Q64">
+        <v>-528.7801177719998</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.4949184469961873</v>
+      </c>
+      <c r="T64">
+        <v>2.662330936562782</v>
+      </c>
+      <c r="U64">
+        <v>0.2138</v>
+      </c>
+      <c r="V64">
+        <v>0.07396436522577438</v>
+      </c>
+      <c r="W64">
+        <v>0.1979864187147294</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3215841966338017</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.3125705894616834</v>
+      </c>
+      <c r="C65">
+        <v>335.1855505519807</v>
+      </c>
+      <c r="D65">
+        <v>5338.788550551981</v>
+      </c>
+      <c r="E65">
+        <v>4591.103</v>
+      </c>
+      <c r="F65">
+        <v>5076.603</v>
+      </c>
+      <c r="G65">
+        <v>73</v>
+      </c>
+      <c r="H65">
+        <v>7572.6</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>372.7</v>
+      </c>
+      <c r="K65">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L65">
+        <v>343.5</v>
+      </c>
+      <c r="M65">
+        <v>1085.3777214</v>
+      </c>
+      <c r="N65">
+        <v>-741.8777213999999</v>
+      </c>
+      <c r="O65">
+        <v>-170.631875922</v>
+      </c>
+      <c r="P65">
+        <v>-571.245845478</v>
+      </c>
+      <c r="Q65">
+        <v>-542.045845478</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.5072459725906788</v>
+      </c>
+      <c r="T65">
+        <v>2.734285826740154</v>
+      </c>
+      <c r="U65">
+        <v>0.2138</v>
+      </c>
+      <c r="V65">
+        <v>0.07279032768250812</v>
+      </c>
+      <c r="W65">
+        <v>0.1982374279414797</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3164796855761223</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.3143205894616834</v>
+      </c>
+      <c r="C66">
+        <v>220.6946348476022</v>
+      </c>
+      <c r="D66">
+        <v>5304.878634847602</v>
+      </c>
+      <c r="E66">
+        <v>4671.684</v>
+      </c>
+      <c r="F66">
+        <v>5157.184</v>
+      </c>
+      <c r="G66">
+        <v>73</v>
+      </c>
+      <c r="H66">
+        <v>7572.6</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>372.7</v>
+      </c>
+      <c r="K66">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L66">
+        <v>343.5</v>
+      </c>
+      <c r="M66">
+        <v>1102.6059392</v>
+      </c>
+      <c r="N66">
+        <v>-759.1059392</v>
+      </c>
+      <c r="O66">
+        <v>-174.594366016</v>
+      </c>
+      <c r="P66">
+        <v>-584.511573184</v>
+      </c>
+      <c r="Q66">
+        <v>-555.3115731840001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.5202583607181976</v>
+      </c>
+      <c r="T66">
+        <v>2.81023821081627</v>
+      </c>
+      <c r="U66">
+        <v>0.2138</v>
+      </c>
+      <c r="V66">
+        <v>0.07165297881246892</v>
+      </c>
+      <c r="W66">
+        <v>0.1984805931298941</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3115346904889953</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.3160705894616834</v>
+      </c>
+      <c r="C67">
+        <v>106.6317656417577</v>
+      </c>
+      <c r="D67">
+        <v>5271.396765641758</v>
+      </c>
+      <c r="E67">
+        <v>4752.265</v>
+      </c>
+      <c r="F67">
+        <v>5237.765</v>
+      </c>
+      <c r="G67">
+        <v>73</v>
+      </c>
+      <c r="H67">
+        <v>7572.6</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>372.7</v>
+      </c>
+      <c r="K67">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L67">
+        <v>343.5</v>
+      </c>
+      <c r="M67">
+        <v>1119.834157</v>
+      </c>
+      <c r="N67">
+        <v>-776.334157</v>
+      </c>
+      <c r="O67">
+        <v>-178.55685611</v>
+      </c>
+      <c r="P67">
+        <v>-597.77730089</v>
+      </c>
+      <c r="Q67">
+        <v>-568.5773008900001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.5340143138815748</v>
+      </c>
+      <c r="T67">
+        <v>2.890530731125307</v>
+      </c>
+      <c r="U67">
+        <v>0.2138</v>
+      </c>
+      <c r="V67">
+        <v>0.07055062529227708</v>
+      </c>
+      <c r="W67">
+        <v>0.1987162763125112</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.306741849096857</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.3178205894616835</v>
+      </c>
+      <c r="C68">
+        <v>-7.011111109599369</v>
+      </c>
+      <c r="D68">
+        <v>5238.334888890401</v>
+      </c>
+      <c r="E68">
+        <v>4832.846</v>
+      </c>
+      <c r="F68">
+        <v>5318.346</v>
+      </c>
+      <c r="G68">
+        <v>73</v>
+      </c>
+      <c r="H68">
+        <v>7572.6</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>372.7</v>
+      </c>
+      <c r="K68">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L68">
+        <v>343.5</v>
+      </c>
+      <c r="M68">
+        <v>1137.0623748</v>
+      </c>
+      <c r="N68">
+        <v>-793.5623748</v>
+      </c>
+      <c r="O68">
+        <v>-182.519346204</v>
+      </c>
+      <c r="P68">
+        <v>-611.0430285960001</v>
+      </c>
+      <c r="Q68">
+        <v>-581.8430285960001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.5485794407604447</v>
+      </c>
+      <c r="T68">
+        <v>2.975546340864286</v>
+      </c>
+      <c r="U68">
+        <v>0.2138</v>
+      </c>
+      <c r="V68">
+        <v>0.06948167642421228</v>
+      </c>
+      <c r="W68">
+        <v>0.1989448175805034</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3020942453226622</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.3195705894616834</v>
+      </c>
+      <c r="C69">
+        <v>-120.2418486520328</v>
+      </c>
+      <c r="D69">
+        <v>5205.685151347968</v>
+      </c>
+      <c r="E69">
+        <v>4913.427000000001</v>
+      </c>
+      <c r="F69">
+        <v>5398.927000000001</v>
+      </c>
+      <c r="G69">
+        <v>73</v>
+      </c>
+      <c r="H69">
+        <v>7572.6</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>372.7</v>
+      </c>
+      <c r="K69">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L69">
+        <v>343.5</v>
+      </c>
+      <c r="M69">
+        <v>1154.2905926</v>
+      </c>
+      <c r="N69">
+        <v>-810.7905926000001</v>
+      </c>
+      <c r="O69">
+        <v>-186.481836298</v>
+      </c>
+      <c r="P69">
+        <v>-624.3087563020001</v>
+      </c>
+      <c r="Q69">
+        <v>-595.1087563020001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.5640273026016702</v>
+      </c>
+      <c r="T69">
+        <v>3.065714411799568</v>
+      </c>
+      <c r="U69">
+        <v>0.2138</v>
+      </c>
+      <c r="V69">
+        <v>0.06844463647758224</v>
+      </c>
+      <c r="W69">
+        <v>0.1991665367210929</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2975853759894881</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.3213205894616834</v>
+      </c>
+      <c r="C70">
+        <v>-233.0681056515905</v>
+      </c>
+      <c r="D70">
+        <v>5173.43989434841</v>
+      </c>
+      <c r="E70">
+        <v>4994.008000000001</v>
+      </c>
+      <c r="F70">
+        <v>5479.508000000001</v>
+      </c>
+      <c r="G70">
+        <v>73</v>
+      </c>
+      <c r="H70">
+        <v>7572.6</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>372.7</v>
+      </c>
+      <c r="K70">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L70">
+        <v>343.5</v>
+      </c>
+      <c r="M70">
+        <v>1171.5188104</v>
+      </c>
+      <c r="N70">
+        <v>-828.0188104000001</v>
+      </c>
+      <c r="O70">
+        <v>-190.444326392</v>
+      </c>
+      <c r="P70">
+        <v>-637.5744840080001</v>
+      </c>
+      <c r="Q70">
+        <v>-608.3744840080001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.5804406558079724</v>
+      </c>
+      <c r="T70">
+        <v>3.161517987168304</v>
+      </c>
+      <c r="U70">
+        <v>0.2138</v>
+      </c>
+      <c r="V70">
+        <v>0.06743809770585309</v>
+      </c>
+      <c r="W70">
+        <v>0.1993817347104886</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2932091204602308</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.3230705894616834</v>
+      </c>
+      <c r="C71">
+        <v>-345.497352184073</v>
+      </c>
+      <c r="D71">
+        <v>5141.591647815928</v>
+      </c>
+      <c r="E71">
+        <v>5074.589000000001</v>
+      </c>
+      <c r="F71">
+        <v>5560.089000000001</v>
+      </c>
+      <c r="G71">
+        <v>73</v>
+      </c>
+      <c r="H71">
+        <v>7572.6</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>372.7</v>
+      </c>
+      <c r="K71">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L71">
+        <v>343.5</v>
+      </c>
+      <c r="M71">
+        <v>1188.7470282</v>
+      </c>
+      <c r="N71">
+        <v>-845.2470282000002</v>
+      </c>
+      <c r="O71">
+        <v>-194.406816486</v>
+      </c>
+      <c r="P71">
+        <v>-650.8402117140001</v>
+      </c>
+      <c r="Q71">
+        <v>-621.6402117140001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.5979129350275845</v>
+      </c>
+      <c r="T71">
+        <v>3.263502438367281</v>
+      </c>
+      <c r="U71">
+        <v>0.2138</v>
+      </c>
+      <c r="V71">
+        <v>0.06646073397098566</v>
+      </c>
+      <c r="W71">
+        <v>0.1995906950770033</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2889597129173289</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.3248205894616835</v>
+      </c>
+      <c r="C72">
+        <v>-457.5368755044146</v>
+      </c>
+      <c r="D72">
+        <v>5110.133124495586</v>
+      </c>
+      <c r="E72">
+        <v>5155.170000000001</v>
+      </c>
+      <c r="F72">
+        <v>5640.670000000001</v>
+      </c>
+      <c r="G72">
+        <v>73</v>
+      </c>
+      <c r="H72">
+        <v>7572.6</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>372.7</v>
+      </c>
+      <c r="K72">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L72">
+        <v>343.5</v>
+      </c>
+      <c r="M72">
+        <v>1205.975246</v>
+      </c>
+      <c r="N72">
+        <v>-862.4752460000002</v>
+      </c>
+      <c r="O72">
+        <v>-198.36930658</v>
+      </c>
+      <c r="P72">
+        <v>-664.1059394200001</v>
+      </c>
+      <c r="Q72">
+        <v>-634.9059394200001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.6165500328618374</v>
+      </c>
+      <c r="T72">
+        <v>3.372285852979525</v>
+      </c>
+      <c r="U72">
+        <v>0.2138</v>
+      </c>
+      <c r="V72">
+        <v>0.06551129491425728</v>
+      </c>
+      <c r="W72">
+        <v>0.1997936851473318</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.28483171701851</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.3265705894616834</v>
+      </c>
+      <c r="C73">
+        <v>-569.1937856055665</v>
+      </c>
+      <c r="D73">
+        <v>5079.057214394434</v>
+      </c>
+      <c r="E73">
+        <v>5235.751</v>
+      </c>
+      <c r="F73">
+        <v>5721.251</v>
+      </c>
+      <c r="G73">
+        <v>73</v>
+      </c>
+      <c r="H73">
+        <v>7572.6</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>372.7</v>
+      </c>
+      <c r="K73">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L73">
+        <v>343.5</v>
+      </c>
+      <c r="M73">
+        <v>1223.2034638</v>
+      </c>
+      <c r="N73">
+        <v>-879.7034638</v>
+      </c>
+      <c r="O73">
+        <v>-202.331796674</v>
+      </c>
+      <c r="P73">
+        <v>-677.371667126</v>
+      </c>
+      <c r="Q73">
+        <v>-648.1716671260001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.6364724477881074</v>
+      </c>
+      <c r="T73">
+        <v>3.488571572047783</v>
+      </c>
+      <c r="U73">
+        <v>0.2138</v>
+      </c>
+      <c r="V73">
+        <v>0.0645886006196903</v>
+      </c>
+      <c r="W73">
+        <v>0.1999909571875102</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2808200026943056</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.3283205894616834</v>
+      </c>
+      <c r="C74">
+        <v>-680.4750205757873</v>
+      </c>
+      <c r="D74">
+        <v>5048.356979424213</v>
+      </c>
+      <c r="E74">
+        <v>5316.332</v>
+      </c>
+      <c r="F74">
+        <v>5801.832</v>
+      </c>
+      <c r="G74">
+        <v>73</v>
+      </c>
+      <c r="H74">
+        <v>7572.6</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>372.7</v>
+      </c>
+      <c r="K74">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L74">
+        <v>343.5</v>
+      </c>
+      <c r="M74">
+        <v>1240.4316816</v>
+      </c>
+      <c r="N74">
+        <v>-896.9316816</v>
+      </c>
+      <c r="O74">
+        <v>-206.294286768</v>
+      </c>
+      <c r="P74">
+        <v>-690.637394832</v>
+      </c>
+      <c r="Q74">
+        <v>-661.4373948320001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.6578178923519684</v>
+      </c>
+      <c r="T74">
+        <v>3.613163413906632</v>
+      </c>
+      <c r="U74">
+        <v>0.2138</v>
+      </c>
+      <c r="V74">
+        <v>0.06369153672219459</v>
+      </c>
+      <c r="W74">
+        <v>0.2001827494487948</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.276919724879107</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.3300705894616834</v>
+      </c>
+      <c r="C75">
+        <v>-791.387351762779</v>
+      </c>
+      <c r="D75">
+        <v>5018.025648237222</v>
+      </c>
+      <c r="E75">
+        <v>5396.913</v>
+      </c>
+      <c r="F75">
+        <v>5882.413</v>
+      </c>
+      <c r="G75">
+        <v>73</v>
+      </c>
+      <c r="H75">
+        <v>7572.6</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>372.7</v>
+      </c>
+      <c r="K75">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L75">
+        <v>343.5</v>
+      </c>
+      <c r="M75">
+        <v>1257.6598994</v>
+      </c>
+      <c r="N75">
+        <v>-914.1598994000001</v>
+      </c>
+      <c r="O75">
+        <v>-210.256776862</v>
+      </c>
+      <c r="P75">
+        <v>-703.903122538</v>
+      </c>
+      <c r="Q75">
+        <v>-674.7031225380001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.6807444809575969</v>
+      </c>
+      <c r="T75">
+        <v>3.74698428108836</v>
+      </c>
+      <c r="U75">
+        <v>0.2138</v>
+      </c>
+      <c r="V75">
+        <v>0.06281904991778096</v>
+      </c>
+      <c r="W75">
+        <v>0.2003692871275784</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2731263039903521</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.3318205894616834</v>
+      </c>
+      <c r="C76">
+        <v>-901.9373887527991</v>
+      </c>
+      <c r="D76">
+        <v>4988.056611247202</v>
+      </c>
+      <c r="E76">
+        <v>5477.494000000001</v>
+      </c>
+      <c r="F76">
+        <v>5962.994000000001</v>
+      </c>
+      <c r="G76">
+        <v>73</v>
+      </c>
+      <c r="H76">
+        <v>7572.6</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>372.7</v>
+      </c>
+      <c r="K76">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L76">
+        <v>343.5</v>
+      </c>
+      <c r="M76">
+        <v>1274.8881172</v>
+      </c>
+      <c r="N76">
+        <v>-931.3881172000001</v>
+      </c>
+      <c r="O76">
+        <v>-214.219266956</v>
+      </c>
+      <c r="P76">
+        <v>-717.1688502440002</v>
+      </c>
+      <c r="Q76">
+        <v>-687.9688502440001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.7054346533021199</v>
+      </c>
+      <c r="T76">
+        <v>3.89109906113022</v>
+      </c>
+      <c r="U76">
+        <v>0.2138</v>
+      </c>
+      <c r="V76">
+        <v>0.06197014383781096</v>
+      </c>
+      <c r="W76">
+        <v>0.200550783247476</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2694354079904824</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.3335705894616834</v>
+      </c>
+      <c r="C77">
+        <v>-1012.131584172412</v>
+      </c>
+      <c r="D77">
+        <v>4958.443415827589</v>
+      </c>
+      <c r="E77">
+        <v>5558.075000000001</v>
+      </c>
+      <c r="F77">
+        <v>6043.575000000001</v>
+      </c>
+      <c r="G77">
+        <v>73</v>
+      </c>
+      <c r="H77">
+        <v>7572.6</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>372.7</v>
+      </c>
+      <c r="K77">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L77">
+        <v>343.5</v>
+      </c>
+      <c r="M77">
+        <v>1292.116335</v>
+      </c>
+      <c r="N77">
+        <v>-948.6163350000002</v>
+      </c>
+      <c r="O77">
+        <v>-218.18175705</v>
+      </c>
+      <c r="P77">
+        <v>-730.4345779500002</v>
+      </c>
+      <c r="Q77">
+        <v>-701.2345779500001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.7321000394342048</v>
+      </c>
+      <c r="T77">
+        <v>4.046743023575429</v>
+      </c>
+      <c r="U77">
+        <v>0.2138</v>
+      </c>
+      <c r="V77">
+        <v>0.06114387525330681</v>
+      </c>
+      <c r="W77">
+        <v>0.200727439470843</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2658429358839427</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.3353205894616835</v>
+      </c>
+      <c r="C78">
+        <v>-1121.976238320176</v>
+      </c>
+      <c r="D78">
+        <v>4929.179761679824</v>
+      </c>
+      <c r="E78">
+        <v>5638.656</v>
+      </c>
+      <c r="F78">
+        <v>6124.156</v>
+      </c>
+      <c r="G78">
+        <v>73</v>
+      </c>
+      <c r="H78">
+        <v>7572.6</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>372.7</v>
+      </c>
+      <c r="K78">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L78">
+        <v>343.5</v>
+      </c>
+      <c r="M78">
+        <v>1309.3445528</v>
+      </c>
+      <c r="N78">
+        <v>-965.8445528</v>
+      </c>
+      <c r="O78">
+        <v>-222.144247144</v>
+      </c>
+      <c r="P78">
+        <v>-743.700305656</v>
+      </c>
+      <c r="Q78">
+        <v>-714.5003056559999</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.7609875410772968</v>
+      </c>
+      <c r="T78">
+        <v>4.215357316224406</v>
+      </c>
+      <c r="U78">
+        <v>0.2138</v>
+      </c>
+      <c r="V78">
+        <v>0.06033935057892119</v>
+      </c>
+      <c r="W78">
+        <v>0.2008994468462267</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2623450025170487</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.3370705894616834</v>
+      </c>
+      <c r="C79">
+        <v>-1231.47750363533</v>
+      </c>
+      <c r="D79">
+        <v>4900.25949636467</v>
+      </c>
+      <c r="E79">
+        <v>5719.237</v>
+      </c>
+      <c r="F79">
+        <v>6204.737</v>
+      </c>
+      <c r="G79">
+        <v>73</v>
+      </c>
+      <c r="H79">
+        <v>7572.6</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>372.7</v>
+      </c>
+      <c r="K79">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L79">
+        <v>343.5</v>
+      </c>
+      <c r="M79">
+        <v>1326.5727706</v>
+      </c>
+      <c r="N79">
+        <v>-983.0727706</v>
+      </c>
+      <c r="O79">
+        <v>-226.106737238</v>
+      </c>
+      <c r="P79">
+        <v>-756.966033362</v>
+      </c>
+      <c r="Q79">
+        <v>-727.7660333619999</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.792386999385005</v>
+      </c>
+      <c r="T79">
+        <v>4.39863372127764</v>
+      </c>
+      <c r="U79">
+        <v>0.2138</v>
+      </c>
+      <c r="V79">
+        <v>0.05955572264932481</v>
+      </c>
+      <c r="W79">
+        <v>0.2010669864975743</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2589379245622818</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.3388205894616835</v>
+      </c>
+      <c r="C80">
+        <v>-1340.641389010049</v>
+      </c>
+      <c r="D80">
+        <v>4871.676610989951</v>
+      </c>
+      <c r="E80">
+        <v>5799.818</v>
+      </c>
+      <c r="F80">
+        <v>6285.318</v>
+      </c>
+      <c r="G80">
+        <v>73</v>
+      </c>
+      <c r="H80">
+        <v>7572.6</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>372.7</v>
+      </c>
+      <c r="K80">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L80">
+        <v>343.5</v>
+      </c>
+      <c r="M80">
+        <v>1343.8009884</v>
+      </c>
+      <c r="N80">
+        <v>-1000.3009884</v>
+      </c>
+      <c r="O80">
+        <v>-230.069227332</v>
+      </c>
+      <c r="P80">
+        <v>-770.2317610680001</v>
+      </c>
+      <c r="Q80">
+        <v>-741.0317610680002</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.8266409539025055</v>
+      </c>
+      <c r="T80">
+        <v>4.598571617699351</v>
+      </c>
+      <c r="U80">
+        <v>0.2138</v>
+      </c>
+      <c r="V80">
+        <v>0.05879218774356425</v>
+      </c>
+      <c r="W80">
+        <v>0.201230230260426</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2556182075807141</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.3405705894616834</v>
+      </c>
+      <c r="C81">
+        <v>-1449.473763951656</v>
+      </c>
+      <c r="D81">
+        <v>4843.425236048344</v>
+      </c>
+      <c r="E81">
+        <v>5880.399</v>
+      </c>
+      <c r="F81">
+        <v>6365.899</v>
+      </c>
+      <c r="G81">
+        <v>73</v>
+      </c>
+      <c r="H81">
+        <v>7572.6</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>372.7</v>
+      </c>
+      <c r="K81">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L81">
+        <v>343.5</v>
+      </c>
+      <c r="M81">
+        <v>1361.0292062</v>
+      </c>
+      <c r="N81">
+        <v>-1017.5292062</v>
+      </c>
+      <c r="O81">
+        <v>-234.031717426</v>
+      </c>
+      <c r="P81">
+        <v>-783.4974887740001</v>
+      </c>
+      <c r="Q81">
+        <v>-754.2974887740002</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.8641571898026248</v>
+      </c>
+      <c r="T81">
+        <v>4.817551218542178</v>
+      </c>
+      <c r="U81">
+        <v>0.2138</v>
+      </c>
+      <c r="V81">
+        <v>0.05804798283541785</v>
+      </c>
+      <c r="W81">
+        <v>0.2013893412697876</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2523825340670341</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.3423205894616834</v>
+      </c>
+      <c r="C82">
+        <v>-1557.980362600886</v>
+      </c>
+      <c r="D82">
+        <v>4815.499637399114</v>
+      </c>
+      <c r="E82">
+        <v>5960.98</v>
+      </c>
+      <c r="F82">
+        <v>6446.48</v>
+      </c>
+      <c r="G82">
+        <v>73</v>
+      </c>
+      <c r="H82">
+        <v>7572.6</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>372.7</v>
+      </c>
+      <c r="K82">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L82">
+        <v>343.5</v>
+      </c>
+      <c r="M82">
+        <v>1378.257424</v>
+      </c>
+      <c r="N82">
+        <v>-1034.757424</v>
+      </c>
+      <c r="O82">
+        <v>-237.99420752</v>
+      </c>
+      <c r="P82">
+        <v>-796.7632164800001</v>
+      </c>
+      <c r="Q82">
+        <v>-767.5632164800002</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.905425049292756</v>
+      </c>
+      <c r="T82">
+        <v>5.058428779469287</v>
+      </c>
+      <c r="U82">
+        <v>0.2138</v>
+      </c>
+      <c r="V82">
+        <v>0.05732238304997513</v>
+      </c>
+      <c r="W82">
+        <v>0.2015444745039153</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2492277523911962</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3440705894616835</v>
+      </c>
+      <c r="C83">
+        <v>-1666.166787611887</v>
+      </c>
+      <c r="D83">
+        <v>4787.894212388113</v>
+      </c>
+      <c r="E83">
+        <v>6041.561000000001</v>
+      </c>
+      <c r="F83">
+        <v>6527.061000000001</v>
+      </c>
+      <c r="G83">
+        <v>73</v>
+      </c>
+      <c r="H83">
+        <v>7572.6</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>372.7</v>
+      </c>
+      <c r="K83">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L83">
+        <v>343.5</v>
+      </c>
+      <c r="M83">
+        <v>1395.4856418</v>
+      </c>
+      <c r="N83">
+        <v>-1051.9856418</v>
+      </c>
+      <c r="O83">
+        <v>-241.956697614</v>
+      </c>
+      <c r="P83">
+        <v>-810.0289441860002</v>
+      </c>
+      <c r="Q83">
+        <v>-780.8289441860002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.9510368939923748</v>
+      </c>
+      <c r="T83">
+        <v>5.324661873125565</v>
+      </c>
+      <c r="U83">
+        <v>0.2138</v>
+      </c>
+      <c r="V83">
+        <v>0.05661469930861741</v>
+      </c>
+      <c r="W83">
+        <v>0.2016957772878176</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2461508665592061</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3458205894616834</v>
+      </c>
+      <c r="C84">
+        <v>-1774.038513899563</v>
+      </c>
+      <c r="D84">
+        <v>4760.603486100438</v>
+      </c>
+      <c r="E84">
+        <v>6122.142000000001</v>
+      </c>
+      <c r="F84">
+        <v>6607.642000000001</v>
+      </c>
+      <c r="G84">
+        <v>73</v>
+      </c>
+      <c r="H84">
+        <v>7572.6</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>372.7</v>
+      </c>
+      <c r="K84">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L84">
+        <v>343.5</v>
+      </c>
+      <c r="M84">
+        <v>1412.7138596</v>
+      </c>
+      <c r="N84">
+        <v>-1069.2138596</v>
+      </c>
+      <c r="O84">
+        <v>-245.919187708</v>
+      </c>
+      <c r="P84">
+        <v>-823.294671892</v>
+      </c>
+      <c r="Q84">
+        <v>-794.094671892</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>1.001716721436396</v>
+      </c>
+      <c r="T84">
+        <v>5.620476421632541</v>
+      </c>
+      <c r="U84">
+        <v>0.2138</v>
+      </c>
+      <c r="V84">
+        <v>0.0559242761463172</v>
+      </c>
+      <c r="W84">
+        <v>0.2018433897599174</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2431490267231183</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3475705894616835</v>
+      </c>
+      <c r="C85">
+        <v>-1881.600892259466</v>
+      </c>
+      <c r="D85">
+        <v>4733.622107740535</v>
+      </c>
+      <c r="E85">
+        <v>6202.723000000001</v>
+      </c>
+      <c r="F85">
+        <v>6688.223000000001</v>
+      </c>
+      <c r="G85">
+        <v>73</v>
+      </c>
+      <c r="H85">
+        <v>7572.6</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>372.7</v>
+      </c>
+      <c r="K85">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L85">
+        <v>343.5</v>
+      </c>
+      <c r="M85">
+        <v>1429.9420774</v>
+      </c>
+      <c r="N85">
+        <v>-1086.4420774</v>
+      </c>
+      <c r="O85">
+        <v>-249.881677802</v>
+      </c>
+      <c r="P85">
+        <v>-836.560399598</v>
+      </c>
+      <c r="Q85">
+        <v>-807.360399598</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>1.05835888152089</v>
+      </c>
+      <c r="T85">
+        <v>5.951092681728574</v>
+      </c>
+      <c r="U85">
+        <v>0.2138</v>
+      </c>
+      <c r="V85">
+        <v>0.05525048968672302</v>
+      </c>
+      <c r="W85">
+        <v>0.2019874453049786</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2402195203770566</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3493205894616834</v>
+      </c>
+      <c r="C86">
+        <v>-1988.859152865295</v>
+      </c>
+      <c r="D86">
+        <v>4706.944847134705</v>
+      </c>
+      <c r="E86">
+        <v>6283.304</v>
+      </c>
+      <c r="F86">
+        <v>6768.804</v>
+      </c>
+      <c r="G86">
+        <v>73</v>
+      </c>
+      <c r="H86">
+        <v>7572.6</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>372.7</v>
+      </c>
+      <c r="K86">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L86">
+        <v>343.5</v>
+      </c>
+      <c r="M86">
+        <v>1447.1702952</v>
+      </c>
+      <c r="N86">
+        <v>-1103.6702952</v>
+      </c>
+      <c r="O86">
+        <v>-253.844167896</v>
+      </c>
+      <c r="P86">
+        <v>-849.826127304</v>
+      </c>
+      <c r="Q86">
+        <v>-820.626127304</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>1.122081311615944</v>
+      </c>
+      <c r="T86">
+        <v>6.323035974336606</v>
+      </c>
+      <c r="U86">
+        <v>0.2138</v>
+      </c>
+      <c r="V86">
+        <v>0.05459274576188108</v>
+      </c>
+      <c r="W86">
+        <v>0.2021280709561098</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2373597641820917</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3510705894616834</v>
+      </c>
+      <c r="C87">
+        <v>-2095.818408648799</v>
+      </c>
+      <c r="D87">
+        <v>4680.566591351201</v>
+      </c>
+      <c r="E87">
+        <v>6363.885</v>
+      </c>
+      <c r="F87">
+        <v>6849.385</v>
+      </c>
+      <c r="G87">
+        <v>73</v>
+      </c>
+      <c r="H87">
+        <v>7572.6</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>372.7</v>
+      </c>
+      <c r="K87">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L87">
+        <v>343.5</v>
+      </c>
+      <c r="M87">
+        <v>1464.398513</v>
+      </c>
+      <c r="N87">
+        <v>-1120.898513</v>
+      </c>
+      <c r="O87">
+        <v>-257.80665799</v>
+      </c>
+      <c r="P87">
+        <v>-863.0918550099999</v>
+      </c>
+      <c r="Q87">
+        <v>-833.89185501</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>1.194300065723674</v>
+      </c>
+      <c r="T87">
+        <v>6.744571705959046</v>
+      </c>
+      <c r="U87">
+        <v>0.2138</v>
+      </c>
+      <c r="V87">
+        <v>0.05395047816468249</v>
+      </c>
+      <c r="W87">
+        <v>0.2022653877683909</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2345672963681847</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3528205894616834</v>
+      </c>
+      <c r="C88">
+        <v>-2202.483658566634</v>
+      </c>
+      <c r="D88">
+        <v>4654.482341433366</v>
+      </c>
+      <c r="E88">
+        <v>6444.466</v>
+      </c>
+      <c r="F88">
+        <v>6929.966</v>
+      </c>
+      <c r="G88">
+        <v>73</v>
+      </c>
+      <c r="H88">
+        <v>7572.6</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>372.7</v>
+      </c>
+      <c r="K88">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L88">
+        <v>343.5</v>
+      </c>
+      <c r="M88">
+        <v>1481.6267308</v>
+      </c>
+      <c r="N88">
+        <v>-1138.1267308</v>
+      </c>
+      <c r="O88">
+        <v>-261.7691480839999</v>
+      </c>
+      <c r="P88">
+        <v>-876.357582716</v>
+      </c>
+      <c r="Q88">
+        <v>-847.157582716</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.276835784703937</v>
+      </c>
+      <c r="T88">
+        <v>7.226326827813264</v>
+      </c>
+      <c r="U88">
+        <v>0.2138</v>
+      </c>
+      <c r="V88">
+        <v>0.05332314702323269</v>
+      </c>
+      <c r="W88">
+        <v>0.2023995111664328</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2318397696662291</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3545705894616834</v>
+      </c>
+      <c r="C89">
+        <v>-2308.85979075863</v>
+      </c>
+      <c r="D89">
+        <v>4628.687209241371</v>
+      </c>
+      <c r="E89">
+        <v>6525.047</v>
+      </c>
+      <c r="F89">
+        <v>7010.547</v>
+      </c>
+      <c r="G89">
+        <v>73</v>
+      </c>
+      <c r="H89">
+        <v>7572.6</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>372.7</v>
+      </c>
+      <c r="K89">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L89">
+        <v>343.5</v>
+      </c>
+      <c r="M89">
+        <v>1498.8549486</v>
+      </c>
+      <c r="N89">
+        <v>-1155.3549486</v>
+      </c>
+      <c r="O89">
+        <v>-265.731638178</v>
+      </c>
+      <c r="P89">
+        <v>-889.623310422</v>
+      </c>
+      <c r="Q89">
+        <v>-860.423310422</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.37206930660424</v>
+      </c>
+      <c r="T89">
+        <v>7.782198122260439</v>
+      </c>
+      <c r="U89">
+        <v>0.2138</v>
+      </c>
+      <c r="V89">
+        <v>0.05271023728733346</v>
+      </c>
+      <c r="W89">
+        <v>0.2025305512679681</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2291749447275369</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3563205894616834</v>
+      </c>
+      <c r="C90">
+        <v>-2414.95158560159</v>
+      </c>
+      <c r="D90">
+        <v>4603.176414398411</v>
+      </c>
+      <c r="E90">
+        <v>6605.628000000001</v>
+      </c>
+      <c r="F90">
+        <v>7091.128000000001</v>
+      </c>
+      <c r="G90">
+        <v>73</v>
+      </c>
+      <c r="H90">
+        <v>7572.6</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>372.7</v>
+      </c>
+      <c r="K90">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L90">
+        <v>343.5</v>
+      </c>
+      <c r="M90">
+        <v>1516.0831664</v>
+      </c>
+      <c r="N90">
+        <v>-1172.5831664</v>
+      </c>
+      <c r="O90">
+        <v>-269.694128272</v>
+      </c>
+      <c r="P90">
+        <v>-902.889038128</v>
+      </c>
+      <c r="Q90">
+        <v>-873.689038128</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.483175082154593</v>
+      </c>
+      <c r="T90">
+        <v>8.43071463244881</v>
+      </c>
+      <c r="U90">
+        <v>0.2138</v>
+      </c>
+      <c r="V90">
+        <v>0.05211125731815921</v>
+      </c>
+      <c r="W90">
+        <v>0.2026586131853775</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2265706839919966</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3580705894616835</v>
+      </c>
+      <c r="C91">
+        <v>-2520.763718662671</v>
+      </c>
+      <c r="D91">
+        <v>4577.94528133733</v>
+      </c>
+      <c r="E91">
+        <v>6686.209000000001</v>
+      </c>
+      <c r="F91">
+        <v>7171.709000000001</v>
+      </c>
+      <c r="G91">
+        <v>73</v>
+      </c>
+      <c r="H91">
+        <v>7572.6</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>372.7</v>
+      </c>
+      <c r="K91">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L91">
+        <v>343.5</v>
+      </c>
+      <c r="M91">
+        <v>1533.3113842</v>
+      </c>
+      <c r="N91">
+        <v>-1189.8113842</v>
+      </c>
+      <c r="O91">
+        <v>-273.656618366</v>
+      </c>
+      <c r="P91">
+        <v>-916.154765834</v>
+      </c>
+      <c r="Q91">
+        <v>-886.954765834</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.614481907805011</v>
+      </c>
+      <c r="T91">
+        <v>9.197143235398702</v>
+      </c>
+      <c r="U91">
+        <v>0.2138</v>
+      </c>
+      <c r="V91">
+        <v>0.05152573757301136</v>
+      </c>
+      <c r="W91">
+        <v>0.2027837973068902</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2240249459696146</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3598205894616834</v>
+      </c>
+      <c r="C92">
+        <v>-2626.300763556159</v>
+      </c>
+      <c r="D92">
+        <v>4552.989236443842</v>
+      </c>
+      <c r="E92">
+        <v>6766.790000000001</v>
+      </c>
+      <c r="F92">
+        <v>7252.290000000001</v>
+      </c>
+      <c r="G92">
+        <v>73</v>
+      </c>
+      <c r="H92">
+        <v>7572.6</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>372.7</v>
+      </c>
+      <c r="K92">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L92">
+        <v>343.5</v>
+      </c>
+      <c r="M92">
+        <v>1550.539602</v>
+      </c>
+      <c r="N92">
+        <v>-1207.039602</v>
+      </c>
+      <c r="O92">
+        <v>-277.61910846</v>
+      </c>
+      <c r="P92">
+        <v>-929.4204935400001</v>
+      </c>
+      <c r="Q92">
+        <v>-900.22049354</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.772050098585512</v>
+      </c>
+      <c r="T92">
+        <v>10.11685755893857</v>
+      </c>
+      <c r="U92">
+        <v>0.2138</v>
+      </c>
+      <c r="V92">
+        <v>0.05095322937775567</v>
+      </c>
+      <c r="W92">
+        <v>0.2029061995590358</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2215357799032855</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3615705894616834</v>
+      </c>
+      <c r="C93">
+        <v>-2731.567194707323</v>
+      </c>
+      <c r="D93">
+        <v>4528.303805292678</v>
+      </c>
+      <c r="E93">
+        <v>6847.371000000001</v>
+      </c>
+      <c r="F93">
+        <v>7332.871000000001</v>
+      </c>
+      <c r="G93">
+        <v>73</v>
+      </c>
+      <c r="H93">
+        <v>7572.6</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>372.7</v>
+      </c>
+      <c r="K93">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L93">
+        <v>343.5</v>
+      </c>
+      <c r="M93">
+        <v>1567.7678198</v>
+      </c>
+      <c r="N93">
+        <v>-1224.2678198</v>
+      </c>
+      <c r="O93">
+        <v>-281.581598554</v>
+      </c>
+      <c r="P93">
+        <v>-942.6862212460001</v>
+      </c>
+      <c r="Q93">
+        <v>-913.486221246</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.964633442872791</v>
+      </c>
+      <c r="T93">
+        <v>11.24095284326508</v>
+      </c>
+      <c r="U93">
+        <v>0.2138</v>
+      </c>
+      <c r="V93">
+        <v>0.05039330378019792</v>
+      </c>
+      <c r="W93">
+        <v>0.2030259116517937</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2191013207834692</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3633205894616834</v>
+      </c>
+      <c r="C94">
+        <v>-2836.567390026817</v>
+      </c>
+      <c r="D94">
+        <v>4503.884609973184</v>
+      </c>
+      <c r="E94">
+        <v>6927.952</v>
+      </c>
+      <c r="F94">
+        <v>7413.452</v>
+      </c>
+      <c r="G94">
+        <v>73</v>
+      </c>
+      <c r="H94">
+        <v>7572.6</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>372.7</v>
+      </c>
+      <c r="K94">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L94">
+        <v>343.5</v>
+      </c>
+      <c r="M94">
+        <v>1584.9960376</v>
+      </c>
+      <c r="N94">
+        <v>-1241.4960376</v>
+      </c>
+      <c r="O94">
+        <v>-285.544088648</v>
+      </c>
+      <c r="P94">
+        <v>-955.951948952</v>
+      </c>
+      <c r="Q94">
+        <v>-926.751948952</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>2.205362623231891</v>
+      </c>
+      <c r="T94">
+        <v>12.64607194867322</v>
+      </c>
+      <c r="U94">
+        <v>0.2138</v>
+      </c>
+      <c r="V94">
+        <v>0.04984555047823926</v>
+      </c>
+      <c r="W94">
+        <v>0.2031430213077524</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2167197846879968</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3650705894616834</v>
+      </c>
+      <c r="C95">
+        <v>-2941.305633499044</v>
+      </c>
+      <c r="D95">
+        <v>4479.727366500956</v>
+      </c>
+      <c r="E95">
+        <v>7008.533</v>
+      </c>
+      <c r="F95">
+        <v>7494.033</v>
+      </c>
+      <c r="G95">
+        <v>73</v>
+      </c>
+      <c r="H95">
+        <v>7572.6</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>372.7</v>
+      </c>
+      <c r="K95">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L95">
+        <v>343.5</v>
+      </c>
+      <c r="M95">
+        <v>1602.2242554</v>
+      </c>
+      <c r="N95">
+        <v>-1258.7242554</v>
+      </c>
+      <c r="O95">
+        <v>-289.506578742</v>
+      </c>
+      <c r="P95">
+        <v>-969.217676658</v>
+      </c>
+      <c r="Q95">
+        <v>-940.017676658</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>2.514871569407876</v>
+      </c>
+      <c r="T95">
+        <v>14.45265365562654</v>
+      </c>
+      <c r="U95">
+        <v>0.2138</v>
+      </c>
+      <c r="V95">
+        <v>0.04930957681718291</v>
+      </c>
+      <c r="W95">
+        <v>0.2032576124764863</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2143894644225344</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3668205894616834</v>
+      </c>
+      <c r="C96">
+        <v>-3045.786117687649</v>
+      </c>
+      <c r="D96">
+        <v>4455.827882312351</v>
+      </c>
+      <c r="E96">
+        <v>7089.114</v>
+      </c>
+      <c r="F96">
+        <v>7574.614</v>
+      </c>
+      <c r="G96">
+        <v>73</v>
+      </c>
+      <c r="H96">
+        <v>7572.6</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>372.7</v>
+      </c>
+      <c r="K96">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L96">
+        <v>343.5</v>
+      </c>
+      <c r="M96">
+        <v>1619.4524732</v>
+      </c>
+      <c r="N96">
+        <v>-1275.9524732</v>
+      </c>
+      <c r="O96">
+        <v>-293.469068836</v>
+      </c>
+      <c r="P96">
+        <v>-982.4834043640001</v>
+      </c>
+      <c r="Q96">
+        <v>-953.283404364</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.927550164309189</v>
+      </c>
+      <c r="T96">
+        <v>16.86142926489763</v>
+      </c>
+      <c r="U96">
+        <v>0.2138</v>
+      </c>
+      <c r="V96">
+        <v>0.04878500685104267</v>
+      </c>
+      <c r="W96">
+        <v>0.203369765535247</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2121087254393159</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3685705894616834</v>
+      </c>
+      <c r="C97">
+        <v>-3150.012946161242</v>
+      </c>
+      <c r="D97">
+        <v>4432.182053838758</v>
+      </c>
+      <c r="E97">
+        <v>7169.695000000001</v>
+      </c>
+      <c r="F97">
+        <v>7655.195000000001</v>
+      </c>
+      <c r="G97">
+        <v>73</v>
+      </c>
+      <c r="H97">
+        <v>7572.6</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>372.7</v>
+      </c>
+      <c r="K97">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L97">
+        <v>343.5</v>
+      </c>
+      <c r="M97">
+        <v>1636.680691</v>
+      </c>
+      <c r="N97">
+        <v>-1293.180691</v>
+      </c>
+      <c r="O97">
+        <v>-297.43155893</v>
+      </c>
+      <c r="P97">
+        <v>-995.7491320700001</v>
+      </c>
+      <c r="Q97">
+        <v>-966.54913207</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>3.505300197171028</v>
+      </c>
+      <c r="T97">
+        <v>20.23371511787717</v>
+      </c>
+      <c r="U97">
+        <v>0.2138</v>
+      </c>
+      <c r="V97">
+        <v>0.04827148046313696</v>
+      </c>
+      <c r="W97">
+        <v>0.2034795574769813</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.209876002013639</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3703205894616834</v>
+      </c>
+      <c r="C98">
+        <v>-3253.990135842289</v>
+      </c>
+      <c r="D98">
+        <v>4408.785864157711</v>
+      </c>
+      <c r="E98">
+        <v>7250.276</v>
+      </c>
+      <c r="F98">
+        <v>7735.776</v>
+      </c>
+      <c r="G98">
+        <v>73</v>
+      </c>
+      <c r="H98">
+        <v>7572.6</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>372.7</v>
+      </c>
+      <c r="K98">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L98">
+        <v>343.5</v>
+      </c>
+      <c r="M98">
+        <v>1653.9089088</v>
+      </c>
+      <c r="N98">
+        <v>-1310.4089088</v>
+      </c>
+      <c r="O98">
+        <v>-301.3940490239999</v>
+      </c>
+      <c r="P98">
+        <v>-1009.014859776</v>
+      </c>
+      <c r="Q98">
+        <v>-979.8148597759998</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>4.371925246463776</v>
+      </c>
+      <c r="T98">
+        <v>25.29214389734641</v>
+      </c>
+      <c r="U98">
+        <v>0.2138</v>
+      </c>
+      <c r="V98">
+        <v>0.04776865254164595</v>
+      </c>
+      <c r="W98">
+        <v>0.2035870620865961</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2076897936593303</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3720705894616834</v>
+      </c>
+      <c r="C99">
+        <v>-3357.721619282001</v>
+      </c>
+      <c r="D99">
+        <v>4385.635380717999</v>
+      </c>
+      <c r="E99">
+        <v>7330.857</v>
+      </c>
+      <c r="F99">
+        <v>7816.357</v>
+      </c>
+      <c r="G99">
+        <v>73</v>
+      </c>
+      <c r="H99">
+        <v>7572.6</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>372.7</v>
+      </c>
+      <c r="K99">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L99">
+        <v>343.5</v>
+      </c>
+      <c r="M99">
+        <v>1671.1371266</v>
+      </c>
+      <c r="N99">
+        <v>-1327.6371266</v>
+      </c>
+      <c r="O99">
+        <v>-305.3565391179999</v>
+      </c>
+      <c r="P99">
+        <v>-1022.280587482</v>
+      </c>
+      <c r="Q99">
+        <v>-993.0805874819998</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>5.816300328618368</v>
+      </c>
+      <c r="T99">
+        <v>33.72285852979521</v>
+      </c>
+      <c r="U99">
+        <v>0.2138</v>
+      </c>
+      <c r="V99">
+        <v>0.04727619220616507</v>
+      </c>
+      <c r="W99">
+        <v>0.2036923501063219</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2055486617659351</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3738205894616834</v>
+      </c>
+      <c r="C100">
+        <v>-3461.211246863932</v>
+      </c>
+      <c r="D100">
+        <v>4362.726753136069</v>
+      </c>
+      <c r="E100">
+        <v>7411.438</v>
+      </c>
+      <c r="F100">
+        <v>7896.938</v>
+      </c>
+      <c r="G100">
+        <v>73</v>
+      </c>
+      <c r="H100">
+        <v>7572.6</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>372.7</v>
+      </c>
+      <c r="K100">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L100">
+        <v>343.5</v>
+      </c>
+      <c r="M100">
+        <v>1688.3653444</v>
+      </c>
+      <c r="N100">
+        <v>-1344.8653444</v>
+      </c>
+      <c r="O100">
+        <v>-309.319029212</v>
+      </c>
+      <c r="P100">
+        <v>-1035.546315188</v>
+      </c>
+      <c r="Q100">
+        <v>-1006.346315188</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>8.705050492927551</v>
+      </c>
+      <c r="T100">
+        <v>50.58428779469281</v>
+      </c>
+      <c r="U100">
+        <v>0.2138</v>
+      </c>
+      <c r="V100">
+        <v>0.04679378208161235</v>
+      </c>
+      <c r="W100">
+        <v>0.2037954893909513</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2034512264417929</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3755705894616834</v>
+      </c>
+      <c r="C101">
+        <v>-3564.462788938855</v>
+      </c>
+      <c r="D101">
+        <v>4340.056211061145</v>
+      </c>
+      <c r="E101">
+        <v>7492.019</v>
+      </c>
+      <c r="F101">
+        <v>7977.519</v>
+      </c>
+      <c r="G101">
+        <v>73</v>
+      </c>
+      <c r="H101">
+        <v>7572.6</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>372.7</v>
+      </c>
+      <c r="K101">
+        <v>29.19999999999999</v>
+      </c>
+      <c r="L101">
+        <v>343.5</v>
+      </c>
+      <c r="M101">
+        <v>1705.5935622</v>
+      </c>
+      <c r="N101">
+        <v>-1362.0935622</v>
+      </c>
+      <c r="O101">
+        <v>-313.281519306</v>
+      </c>
+      <c r="P101">
+        <v>-1048.812042894</v>
+      </c>
+      <c r="Q101">
+        <v>-1019.612042894</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>17.3713009858551</v>
+      </c>
+      <c r="T101">
+        <v>101.1685755893856</v>
+      </c>
+      <c r="U101">
+        <v>0.2138</v>
+      </c>
+      <c r="V101">
+        <v>0.04632111761614152</v>
+      </c>
+      <c r="W101">
+        <v>0.2038965450536689</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2013961635484415</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
